--- a/docs/data/jp/xlsx/6832.xlsx
+++ b/docs/data/jp/xlsx/6832.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC192"/>
+  <dimension ref="A1:AC199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4343,10 +4346,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>2598</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4381,7 +4386,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>12000000</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5580,7 +5587,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5832,1472 +5839,1614 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>8038.769</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>7526.212</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>7881.669</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>7132.125</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>7742.236</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>7196.492</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>7693.78</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>7725.742</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>8099.73</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>7891.948</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>8511.236000000001</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>8810.173000000001</v>
       </c>
-      <c r="T79" s="22" t="n">
+      <c r="T80" s="22" t="n">
         <v>9113.052</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>7738.254</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>7881.669</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>7693.78</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>8511.236000000001</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>711.876</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>915.427</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>541.356</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>1433.956</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>1343.05</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>1455.941</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>977.097</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>1591.525</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>1743.64</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>1432.504</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>1326.985</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>2150.976</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T81" s="12" t="n">
         <v>1727.736</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>137.537</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>541.356</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>977.097</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>1326.985</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>1070.016</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>1068.343</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>1148.244</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>1072.577</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>1165.346</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>1233.523</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>1299.758</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>1368.076</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>1491.541</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>1480.11</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>1448.571</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>1625.292</v>
-      </c>
-      <c r="T81" s="22" t="n">
-        <v>1110.103</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>1058.27</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>1148.244</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>1299.758</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>1448.571</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>-358.14</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>-152.917</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>-606.888</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>361.378</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>177.705</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>222.417</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>-322.661</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>223.449</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>252.099</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>-47.606</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>-121.586</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>525.684</v>
-      </c>
-      <c r="T82" s="12" t="n">
-        <v>617.633</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>-920.732</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>-606.888</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>-322.661</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>-121.586</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="17">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>0.554</v>
+        <v>1070.016</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>0.342</v>
+        <v>1068.343</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>1.105</v>
+        <v>1148.244</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>0.8090000000000001</v>
+        <v>1072.577</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>2.271</v>
+        <v>1165.346</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>3.436</v>
+        <v>1233.523</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>9.625999999999999</v>
+        <v>1299.758</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>13.144</v>
+        <v>1368.076</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>15.779</v>
+        <v>1491.541</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>10.742</v>
+        <v>1480.11</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>12.296</v>
+        <v>1448.571</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>1.895</v>
+        <v>1625.292</v>
       </c>
       <c r="T83" s="22" t="n">
-        <v>0.58</v>
+        <v>1110.103</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>0.548</v>
+        <v>1058.27</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>1.105</v>
+        <v>1148.244</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>9.625999999999999</v>
+        <v>1299.758</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>12.296</v>
+        <v>1448.571</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>배당금수익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>40.383</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>8.349</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>9.157999999999999</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>35.413</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>11.755</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>11.057</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>35.264</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>14.013</v>
-      </c>
-      <c r="T84" s="22" t="n">
-        <v>60.33</v>
-      </c>
-      <c r="U84" s="22" t="n">
-        <v>70.402</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>40.383</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>35.413</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>35.264</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>-358.14</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>-152.917</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>-606.888</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>361.378</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>177.705</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>222.417</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>-322.661</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>223.449</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>252.099</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>-47.606</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>-121.586</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>525.684</v>
+      </c>
+      <c r="T84" s="12" t="n">
+        <v>617.633</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>-920.732</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>-606.888</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>-322.661</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>-121.586</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>외환차익</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>25.928</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>-43.291</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>56.484</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>41.981</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>-41.981</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>6.978</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>-6.978</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>33.441</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>44.221</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>24.146</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>5.092</v>
-      </c>
-      <c r="T85" s="22" t="n">
-        <v>170.431</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>35.117</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>56.484</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>-6.978</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>24.146</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="17">
+        <f>IF(OR(T84="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T84/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>임대료 수익</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>7.737</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>7.737</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>8.186999999999999</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>8.781000000000001</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>6.795</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>7.065</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>6.105</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>13.823</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>10.805</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>6.753</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>6.855</v>
-      </c>
-      <c r="T86" s="22" t="n">
-        <v>8.617000000000001</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>7.737</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>8.186999999999999</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>7.065</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>6.753</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T86" s="17">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
-        </is>
+          <t>이자수익</t>
+        </is>
+      </c>
+      <c r="C87" s="22" t="n">
+        <v>0.554</v>
       </c>
       <c r="D87" s="22" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>5.113</v>
+        <v>1.105</v>
+      </c>
+      <c r="F87" s="22" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="G87" s="22" t="n">
+        <v>2.271</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>0</v>
+        <v>3.436</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>0</v>
+        <v>9.625999999999999</v>
+      </c>
+      <c r="J87" s="22" t="n">
+        <v>13.144</v>
+      </c>
+      <c r="K87" s="22" t="n">
+        <v>15.779</v>
+      </c>
+      <c r="L87" s="22" t="n">
+        <v>10.742</v>
+      </c>
+      <c r="M87" s="22" t="n">
+        <v>12.296</v>
+      </c>
+      <c r="N87" s="22" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="T87" s="22" t="n">
+        <v>0.58</v>
       </c>
       <c r="U87" s="22" t="n">
-        <v>13.997</v>
+        <v>0.548</v>
       </c>
       <c r="V87" s="22" t="n">
-        <v>5.113</v>
+        <v>1.105</v>
       </c>
       <c r="W87" s="22" t="n">
-        <v>0</v>
+        <v>9.625999999999999</v>
+      </c>
+      <c r="X87" s="22" t="n">
+        <v>12.296</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>보상금 수취</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>0.097</v>
+        <v>0.383</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>14.49</v>
+        <v>8.07</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>22.766</v>
+        <v>40.383</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>0.696</v>
+        <v>8.349</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>8.862</v>
+        <v>0.399</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>0</v>
+        <v>9.157999999999999</v>
       </c>
       <c r="I88" s="22" t="n">
-        <v>29.659</v>
+        <v>35.413</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>13.82</v>
+        <v>11.755</v>
       </c>
       <c r="K88" s="22" t="n">
-        <v>6.804</v>
+        <v>0.438</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>2.802</v>
+        <v>11.057</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>0</v>
+        <v>35.264</v>
       </c>
       <c r="N88" s="22" t="n">
-        <v>6.171</v>
+        <v>14.013</v>
       </c>
       <c r="T88" s="22" t="n">
-        <v>0.262</v>
+        <v>60.33</v>
       </c>
       <c r="U88" s="22" t="n">
-        <v>0.035</v>
+        <v>70.402</v>
       </c>
       <c r="V88" s="22" t="n">
-        <v>22.766</v>
+        <v>40.383</v>
       </c>
       <c r="W88" s="22" t="n">
-        <v>29.659</v>
+        <v>35.413</v>
       </c>
       <c r="X88" s="22" t="n">
-        <v>0</v>
+        <v>35.264</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>Technical Support Fee NOI</t>
+          <t>외환차익</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>14.156</v>
+        <v>25.928</v>
       </c>
       <c r="D89" s="22" t="n">
-        <v>35.425</v>
+        <v>-43.291</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>9.326000000000001</v>
+        <v>56.484</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>1.519</v>
+        <v>41.981</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>5.078</v>
+        <v>-41.981</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>9.75</v>
+        <v>6.978</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>5.876</v>
+        <v>-6.978</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>25.6</v>
+        <v>0</v>
       </c>
       <c r="K89" s="22" t="n">
-        <v>18.06</v>
+        <v>33.441</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>186.563</v>
+        <v>44.221</v>
       </c>
       <c r="M89" s="22" t="n">
-        <v>8.583</v>
+        <v>24.146</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>6.778</v>
+        <v>5.092</v>
       </c>
       <c r="T89" s="22" t="n">
-        <v>12.44</v>
+        <v>170.431</v>
       </c>
       <c r="U89" s="22" t="n">
-        <v>14.988</v>
+        <v>35.117</v>
       </c>
       <c r="V89" s="22" t="n">
-        <v>9.326000000000001</v>
+        <v>56.484</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>5.876</v>
+        <v>-6.978</v>
       </c>
       <c r="X89" s="22" t="n">
-        <v>8.583</v>
+        <v>24.146</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>지분법이익</t>
+          <t>임대료 수익</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>0</v>
+        <v>7.737</v>
       </c>
       <c r="D90" s="22" t="n">
-        <v>0</v>
+        <v>7.737</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>0</v>
+        <v>8.186999999999999</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>0.923</v>
+        <v>8.18</v>
       </c>
       <c r="G90" s="22" t="n">
-        <v>9.967000000000001</v>
+        <v>8.781000000000001</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>5.802</v>
+        <v>6.795</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>-5.478</v>
+        <v>7.065</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>0</v>
+        <v>6.105</v>
       </c>
       <c r="K90" s="22" t="n">
-        <v>0</v>
+        <v>13.823</v>
       </c>
       <c r="L90" s="22" t="n">
-        <v>0</v>
+        <v>10.805</v>
       </c>
       <c r="M90" s="22" t="n">
-        <v>0</v>
+        <v>6.753</v>
+      </c>
+      <c r="N90" s="22" t="n">
+        <v>6.855</v>
       </c>
       <c r="T90" s="22" t="n">
-        <v>8.752000000000001</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="U90" s="22" t="n">
-        <v>0</v>
+        <v>7.737</v>
       </c>
       <c r="V90" s="22" t="n">
-        <v>0</v>
+        <v>8.186999999999999</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>-5.478</v>
+        <v>7.065</v>
       </c>
       <c r="X90" s="22" t="n">
-        <v>0</v>
+        <v>6.753</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C91" s="22" t="n">
-        <v>-7.186</v>
+          <t>보조금 수입</t>
+        </is>
       </c>
       <c r="D91" s="22" t="n">
-        <v>16.661</v>
+        <v>0</v>
       </c>
       <c r="E91" s="22" t="n">
-        <v>11.168</v>
-      </c>
-      <c r="F91" s="22" t="n">
-        <v>30.929</v>
-      </c>
-      <c r="G91" s="22" t="n">
-        <v>15.192</v>
+        <v>5.113</v>
       </c>
       <c r="H91" s="22" t="n">
-        <v>28.573</v>
+        <v>0</v>
       </c>
       <c r="I91" s="22" t="n">
-        <v>-8.787000000000001</v>
-      </c>
-      <c r="J91" s="22" t="n">
-        <v>16.183</v>
-      </c>
-      <c r="K91" s="22" t="n">
-        <v>17.306</v>
-      </c>
-      <c r="L91" s="22" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="M91" s="22" t="n">
-        <v>18.121</v>
-      </c>
-      <c r="N91" s="22" t="n">
-        <v>14.635</v>
-      </c>
-      <c r="T91" s="22" t="n">
-        <v>7.447</v>
+        <v>0</v>
       </c>
       <c r="U91" s="22" t="n">
-        <v>3.173</v>
+        <v>13.997</v>
       </c>
       <c r="V91" s="22" t="n">
-        <v>11.168</v>
+        <v>5.113</v>
       </c>
       <c r="W91" s="22" t="n">
-        <v>-8.787000000000001</v>
-      </c>
-      <c r="X91" s="22" t="n">
-        <v>18.121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>보상금 수취</t>
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>66.45399999999999</v>
+        <v>0.097</v>
       </c>
       <c r="D92" s="22" t="n">
-        <v>39.433</v>
+        <v>14.49</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>154.532</v>
+        <v>22.766</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>93.39100000000001</v>
+        <v>0.696</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>8.567</v>
+        <v>8.862</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>70.49299999999999</v>
+        <v>0</v>
       </c>
       <c r="I92" s="22" t="n">
-        <v>66.396</v>
+        <v>29.659</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>86.60899999999999</v>
+        <v>13.82</v>
       </c>
       <c r="K92" s="22" t="n">
-        <v>105.652</v>
+        <v>6.804</v>
       </c>
       <c r="L92" s="22" t="n">
-        <v>282.05</v>
+        <v>2.802</v>
       </c>
       <c r="M92" s="22" t="n">
-        <v>105.164</v>
+        <v>0</v>
       </c>
       <c r="N92" s="22" t="n">
-        <v>55.44</v>
+        <v>6.171</v>
       </c>
       <c r="T92" s="22" t="n">
-        <v>627.444</v>
+        <v>0.262</v>
       </c>
       <c r="U92" s="22" t="n">
-        <v>145.998</v>
+        <v>0.035</v>
       </c>
       <c r="V92" s="22" t="n">
-        <v>154.532</v>
+        <v>22.766</v>
       </c>
       <c r="W92" s="22" t="n">
-        <v>66.396</v>
+        <v>29.659</v>
       </c>
       <c r="X92" s="22" t="n">
-        <v>105.164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>Technical Support Fee NOI</t>
         </is>
       </c>
       <c r="C93" s="22" t="n">
-        <v>1.032</v>
+        <v>14.156</v>
       </c>
       <c r="D93" s="22" t="n">
-        <v>1.069</v>
+        <v>35.425</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>1.238</v>
+        <v>9.326000000000001</v>
       </c>
       <c r="F93" s="22" t="n">
-        <v>1.288</v>
+        <v>1.519</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>1.641</v>
+        <v>5.078</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>1.668</v>
+        <v>9.75</v>
       </c>
       <c r="I93" s="22" t="n">
-        <v>2.041</v>
+        <v>5.876</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>4.397</v>
+        <v>25.6</v>
       </c>
       <c r="K93" s="22" t="n">
-        <v>12.732</v>
+        <v>18.06</v>
       </c>
       <c r="L93" s="22" t="n">
-        <v>24.29</v>
+        <v>186.563</v>
       </c>
       <c r="M93" s="22" t="n">
-        <v>37.071</v>
+        <v>8.583</v>
       </c>
       <c r="N93" s="22" t="n">
-        <v>36.364</v>
+        <v>6.778</v>
       </c>
       <c r="T93" s="22" t="n">
-        <v>3.102</v>
+        <v>12.44</v>
       </c>
       <c r="U93" s="22" t="n">
-        <v>0.8179999999999999</v>
+        <v>14.988</v>
       </c>
       <c r="V93" s="22" t="n">
-        <v>1.238</v>
+        <v>9.326000000000001</v>
       </c>
       <c r="W93" s="22" t="n">
-        <v>2.041</v>
+        <v>5.876</v>
       </c>
       <c r="X93" s="22" t="n">
-        <v>37.071</v>
+        <v>8.583</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
-        </is>
+          <t>지분법이익</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="22" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="G94" s="22" t="n">
+        <v>9.967000000000001</v>
+      </c>
+      <c r="H94" s="22" t="n">
+        <v>5.802</v>
+      </c>
+      <c r="I94" s="22" t="n">
+        <v>-5.478</v>
+      </c>
+      <c r="J94" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G94" s="22" t="n">
-        <v>69.651</v>
-      </c>
-      <c r="J94" s="22" t="n">
-        <v>20.11</v>
-      </c>
       <c r="K94" s="22" t="n">
-        <v>-20.11</v>
-      </c>
-      <c r="N94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" s="22" t="n">
+        <v>8.752000000000001</v>
+      </c>
+      <c r="U94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" s="22" t="n">
+        <v>-5.478</v>
+      </c>
+      <c r="X94" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>보상비 지급</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C95" s="22" t="n">
-        <v>10.917</v>
+        <v>-7.186</v>
       </c>
       <c r="D95" s="22" t="n">
-        <v>21.757</v>
+        <v>16.661</v>
       </c>
       <c r="E95" s="22" t="n">
-        <v>42.38</v>
+        <v>11.168</v>
       </c>
       <c r="F95" s="22" t="n">
-        <v>4.509</v>
+        <v>30.929</v>
       </c>
       <c r="G95" s="22" t="n">
-        <v>1.977</v>
+        <v>15.192</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>17.445</v>
+        <v>28.573</v>
       </c>
       <c r="I95" s="22" t="n">
-        <v>22.895</v>
+        <v>-8.787000000000001</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>4.172</v>
+        <v>16.183</v>
       </c>
       <c r="K95" s="22" t="n">
-        <v>3.513</v>
+        <v>17.306</v>
       </c>
       <c r="L95" s="22" t="n">
-        <v>0</v>
+        <v>15.86</v>
       </c>
       <c r="M95" s="22" t="n">
-        <v>1.014</v>
+        <v>18.121</v>
       </c>
       <c r="N95" s="22" t="n">
-        <v>94</v>
+        <v>14.635</v>
       </c>
       <c r="T95" s="22" t="n">
-        <v>70.20999999999999</v>
+        <v>7.447</v>
       </c>
       <c r="U95" s="22" t="n">
-        <v>1.763</v>
+        <v>3.173</v>
       </c>
       <c r="V95" s="22" t="n">
-        <v>42.38</v>
+        <v>11.168</v>
       </c>
       <c r="W95" s="22" t="n">
-        <v>22.895</v>
+        <v>-8.787000000000001</v>
       </c>
       <c r="X95" s="22" t="n">
-        <v>1.014</v>
+        <v>18.121</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>Depreciation Of Assets For Rent NOE</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C96" s="22" t="n">
-        <v>8.632</v>
+        <v>66.45399999999999</v>
       </c>
       <c r="D96" s="22" t="n">
-        <v>9.827</v>
+        <v>39.433</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>5.136</v>
+        <v>154.532</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>7.613</v>
+        <v>93.39100000000001</v>
       </c>
       <c r="G96" s="22" t="n">
-        <v>8.836</v>
+        <v>8.567</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>7.831</v>
+        <v>70.49299999999999</v>
       </c>
       <c r="I96" s="22" t="n">
-        <v>7.473</v>
+        <v>66.396</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>8.519</v>
+        <v>86.60899999999999</v>
       </c>
       <c r="K96" s="22" t="n">
-        <v>9.316000000000001</v>
+        <v>105.652</v>
       </c>
       <c r="L96" s="22" t="n">
-        <v>7.936</v>
+        <v>282.05</v>
       </c>
       <c r="M96" s="22" t="n">
-        <v>7.369</v>
+        <v>105.164</v>
       </c>
       <c r="N96" s="22" t="n">
-        <v>7.411</v>
+        <v>55.44</v>
       </c>
       <c r="T96" s="22" t="n">
-        <v>7.455</v>
+        <v>627.444</v>
       </c>
       <c r="U96" s="22" t="n">
-        <v>8.641999999999999</v>
+        <v>145.998</v>
       </c>
       <c r="V96" s="22" t="n">
-        <v>5.136</v>
+        <v>154.532</v>
       </c>
       <c r="W96" s="22" t="n">
-        <v>7.473</v>
+        <v>66.396</v>
       </c>
       <c r="X96" s="22" t="n">
-        <v>7.369</v>
+        <v>105.164</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>지분법손실</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C97" s="22" t="n">
-        <v>7.204</v>
+        <v>1.032</v>
       </c>
       <c r="D97" s="22" t="n">
-        <v>3.224</v>
+        <v>1.069</v>
       </c>
       <c r="E97" s="22" t="n">
-        <v>-10.547</v>
+        <v>1.238</v>
       </c>
       <c r="F97" s="22" t="n">
-        <v>0</v>
+        <v>1.288</v>
       </c>
       <c r="G97" s="22" t="n">
-        <v>0</v>
+        <v>1.641</v>
       </c>
       <c r="H97" s="22" t="n">
-        <v>0</v>
+        <v>1.668</v>
       </c>
       <c r="I97" s="22" t="n">
-        <v>0</v>
+        <v>2.041</v>
       </c>
       <c r="J97" s="22" t="n">
-        <v>13.457</v>
+        <v>4.397</v>
       </c>
       <c r="K97" s="22" t="n">
-        <v>1.289</v>
+        <v>12.732</v>
       </c>
       <c r="L97" s="22" t="n">
-        <v>2.351</v>
+        <v>24.29</v>
       </c>
       <c r="M97" s="22" t="n">
-        <v>-15.764</v>
+        <v>37.071</v>
       </c>
       <c r="N97" s="22" t="n">
-        <v>11.142</v>
+        <v>36.364</v>
       </c>
       <c r="T97" s="22" t="n">
-        <v>0</v>
+        <v>3.102</v>
       </c>
       <c r="U97" s="22" t="n">
-        <v>0.675</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="V97" s="22" t="n">
-        <v>-10.547</v>
+        <v>1.238</v>
       </c>
       <c r="W97" s="22" t="n">
-        <v>0</v>
+        <v>2.041</v>
       </c>
       <c r="X97" s="22" t="n">
-        <v>-15.764</v>
+        <v>37.071</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C98" s="22" t="n">
-        <v>3.764</v>
-      </c>
-      <c r="D98" s="22" t="n">
-        <v>1.332</v>
-      </c>
-      <c r="E98" s="22" t="n">
-        <v>-0.573</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F98" s="22" t="n">
-        <v>4.615</v>
+        <v>0</v>
       </c>
       <c r="G98" s="22" t="n">
-        <v>3.274</v>
-      </c>
-      <c r="H98" s="22" t="n">
-        <v>7.823</v>
-      </c>
-      <c r="I98" s="22" t="n">
-        <v>3.46</v>
+        <v>69.651</v>
       </c>
       <c r="J98" s="22" t="n">
-        <v>5.951</v>
+        <v>20.11</v>
       </c>
       <c r="K98" s="22" t="n">
-        <v>7.943</v>
-      </c>
-      <c r="L98" s="22" t="n">
-        <v>11.327</v>
-      </c>
-      <c r="M98" s="22" t="n">
-        <v>10.625</v>
+        <v>-20.11</v>
       </c>
       <c r="N98" s="22" t="n">
-        <v>19.348</v>
-      </c>
-      <c r="T98" s="22" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="U98" s="22" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="V98" s="22" t="n">
-        <v>-0.573</v>
-      </c>
-      <c r="W98" s="22" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="X98" s="22" t="n">
-        <v>10.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>보상비 지급</t>
         </is>
       </c>
       <c r="C99" s="22" t="n">
-        <v>31.55</v>
+        <v>10.917</v>
       </c>
       <c r="D99" s="22" t="n">
-        <v>37.208</v>
+        <v>21.757</v>
       </c>
       <c r="E99" s="22" t="n">
-        <v>37.633</v>
+        <v>42.38</v>
       </c>
       <c r="F99" s="22" t="n">
-        <v>18.027</v>
+        <v>4.509</v>
       </c>
       <c r="G99" s="22" t="n">
-        <v>85.38</v>
+        <v>1.977</v>
       </c>
       <c r="H99" s="22" t="n">
-        <v>-34.885</v>
+        <v>17.445</v>
       </c>
       <c r="I99" s="22" t="n">
-        <v>189.989</v>
+        <v>22.895</v>
       </c>
       <c r="J99" s="22" t="n">
-        <v>56.61</v>
+        <v>4.172</v>
       </c>
       <c r="K99" s="22" t="n">
-        <v>14.681</v>
+        <v>3.513</v>
       </c>
       <c r="L99" s="22" t="n">
-        <v>45.904</v>
+        <v>0</v>
       </c>
       <c r="M99" s="22" t="n">
-        <v>40.315</v>
+        <v>1.014</v>
       </c>
       <c r="N99" s="22" t="n">
-        <v>168.266</v>
+        <v>94</v>
       </c>
       <c r="T99" s="22" t="n">
-        <v>81.16</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="U99" s="22" t="n">
-        <v>12.858</v>
+        <v>1.763</v>
       </c>
       <c r="V99" s="22" t="n">
-        <v>37.633</v>
+        <v>42.38</v>
       </c>
       <c r="W99" s="22" t="n">
-        <v>189.989</v>
+        <v>22.895</v>
       </c>
       <c r="X99" s="22" t="n">
-        <v>40.315</v>
+        <v>1.014</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C100" s="12" t="n">
-        <v>-323.236</v>
-      </c>
-      <c r="D100" s="12" t="n">
-        <v>-150.692</v>
-      </c>
-      <c r="E100" s="12" t="n">
-        <v>-489.989</v>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>436.742</v>
-      </c>
-      <c r="G100" s="12" t="n">
-        <v>100.892</v>
-      </c>
-      <c r="H100" s="12" t="n">
-        <v>327.795</v>
-      </c>
-      <c r="I100" s="12" t="n">
-        <v>-446.254</v>
-      </c>
-      <c r="J100" s="12" t="n">
-        <v>253.448</v>
-      </c>
-      <c r="K100" s="12" t="n">
-        <v>343.069</v>
-      </c>
-      <c r="L100" s="12" t="n">
-        <v>188.541</v>
-      </c>
-      <c r="M100" s="12" t="n">
-        <v>-56.738</v>
-      </c>
-      <c r="N100" s="12" t="n">
-        <v>412.858</v>
-      </c>
-      <c r="T100" s="12" t="n">
-        <v>1163.918</v>
-      </c>
-      <c r="U100" s="12" t="n">
-        <v>-787.593</v>
-      </c>
-      <c r="V100" s="12" t="n">
-        <v>-489.989</v>
-      </c>
-      <c r="W100" s="12" t="n">
-        <v>-446.254</v>
-      </c>
-      <c r="X100" s="12" t="n">
-        <v>-56.738</v>
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>Depreciation Of Assets For Rent NOE</t>
+        </is>
+      </c>
+      <c r="C100" s="22" t="n">
+        <v>8.632</v>
+      </c>
+      <c r="D100" s="22" t="n">
+        <v>9.827</v>
+      </c>
+      <c r="E100" s="22" t="n">
+        <v>5.136</v>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>7.613</v>
+      </c>
+      <c r="G100" s="22" t="n">
+        <v>8.836</v>
+      </c>
+      <c r="H100" s="22" t="n">
+        <v>7.831</v>
+      </c>
+      <c r="I100" s="22" t="n">
+        <v>7.473</v>
+      </c>
+      <c r="J100" s="22" t="n">
+        <v>8.519</v>
+      </c>
+      <c r="K100" s="22" t="n">
+        <v>9.316000000000001</v>
+      </c>
+      <c r="L100" s="22" t="n">
+        <v>7.936</v>
+      </c>
+      <c r="M100" s="22" t="n">
+        <v>7.369</v>
+      </c>
+      <c r="N100" s="22" t="n">
+        <v>7.411</v>
+      </c>
+      <c r="T100" s="22" t="n">
+        <v>7.455</v>
+      </c>
+      <c r="U100" s="22" t="n">
+        <v>8.641999999999999</v>
+      </c>
+      <c r="V100" s="22" t="n">
+        <v>5.136</v>
+      </c>
+      <c r="W100" s="22" t="n">
+        <v>7.473</v>
+      </c>
+      <c r="X100" s="22" t="n">
+        <v>7.369</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각이익</t>
+          <t>지분법손실</t>
         </is>
       </c>
       <c r="C101" s="22" t="n">
-        <v>52.689</v>
+        <v>7.204</v>
       </c>
       <c r="D101" s="22" t="n">
-        <v>7.671</v>
+        <v>3.224</v>
       </c>
       <c r="E101" s="22" t="n">
-        <v>2.483</v>
+        <v>-10.547</v>
       </c>
       <c r="F101" s="22" t="n">
-        <v>0.282</v>
+        <v>0</v>
       </c>
       <c r="G101" s="22" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="H101" s="22" t="n">
-        <v>0.163</v>
+        <v>0</v>
       </c>
       <c r="I101" s="22" t="n">
-        <v>0.662</v>
+        <v>0</v>
       </c>
       <c r="J101" s="22" t="n">
-        <v>0.494</v>
+        <v>13.457</v>
       </c>
       <c r="K101" s="22" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="L101" s="22" t="n">
+        <v>2.351</v>
+      </c>
+      <c r="M101" s="22" t="n">
+        <v>-15.764</v>
+      </c>
+      <c r="N101" s="22" t="n">
+        <v>11.142</v>
+      </c>
+      <c r="T101" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="L101" s="22" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="M101" s="22" t="n">
+      <c r="U101" s="22" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="V101" s="22" t="n">
+        <v>-10.547</v>
+      </c>
+      <c r="W101" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="N101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" s="22" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="U101" s="22" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="V101" s="22" t="n">
-        <v>2.483</v>
-      </c>
-      <c r="W101" s="22" t="n">
-        <v>0.662</v>
-      </c>
       <c r="X101" s="22" t="n">
-        <v>0</v>
+        <v>-15.764</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각이익</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C102" s="22" t="n">
+        <v>3.764</v>
       </c>
       <c r="D102" s="22" t="n">
-        <v>0.953</v>
+        <v>1.332</v>
       </c>
       <c r="E102" s="22" t="n">
-        <v>0</v>
+        <v>-0.573</v>
+      </c>
+      <c r="F102" s="22" t="n">
+        <v>4.615</v>
+      </c>
+      <c r="G102" s="22" t="n">
+        <v>3.274</v>
       </c>
       <c r="H102" s="22" t="n">
-        <v>0</v>
+        <v>7.823</v>
       </c>
       <c r="I102" s="22" t="n">
-        <v>14.385</v>
+        <v>3.46</v>
+      </c>
+      <c r="J102" s="22" t="n">
+        <v>5.951</v>
+      </c>
+      <c r="K102" s="22" t="n">
+        <v>7.943</v>
+      </c>
+      <c r="L102" s="22" t="n">
+        <v>11.327</v>
+      </c>
+      <c r="M102" s="22" t="n">
+        <v>10.625</v>
+      </c>
+      <c r="N102" s="22" t="n">
+        <v>19.348</v>
+      </c>
+      <c r="T102" s="22" t="n">
+        <v>0.393</v>
       </c>
       <c r="U102" s="22" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="V102" s="22" t="n">
-        <v>0</v>
+        <v>-0.573</v>
       </c>
       <c r="W102" s="22" t="n">
-        <v>14.385</v>
+        <v>3.46</v>
+      </c>
+      <c r="X102" s="22" t="n">
+        <v>10.625</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20" t="inlineStr">
         <is>
-          <t>특별이익 합계</t>
+          <t>영업외비용 합계</t>
         </is>
       </c>
       <c r="C103" s="22" t="n">
-        <v>52.777</v>
+        <v>31.55</v>
       </c>
       <c r="D103" s="22" t="n">
-        <v>8.622999999999999</v>
+        <v>37.208</v>
       </c>
       <c r="E103" s="22" t="n">
-        <v>2.483</v>
+        <v>37.633</v>
       </c>
       <c r="F103" s="22" t="n">
-        <v>0.282</v>
+        <v>18.027</v>
       </c>
       <c r="G103" s="22" t="n">
-        <v>0.039</v>
+        <v>85.38</v>
       </c>
       <c r="H103" s="22" t="n">
-        <v>0.163</v>
+        <v>-34.885</v>
       </c>
       <c r="I103" s="22" t="n">
-        <v>15.047</v>
+        <v>189.989</v>
       </c>
       <c r="J103" s="22" t="n">
-        <v>0.494</v>
+        <v>56.61</v>
       </c>
       <c r="K103" s="22" t="n">
-        <v>0</v>
+        <v>14.681</v>
       </c>
       <c r="L103" s="22" t="n">
-        <v>0.407</v>
+        <v>45.904</v>
       </c>
       <c r="M103" s="22" t="n">
-        <v>6.52</v>
+        <v>40.315</v>
       </c>
       <c r="N103" s="22" t="n">
-        <v>0</v>
+        <v>168.266</v>
       </c>
       <c r="T103" s="22" t="n">
-        <v>0.161</v>
+        <v>81.16</v>
       </c>
       <c r="U103" s="22" t="n">
-        <v>0.008</v>
+        <v>12.858</v>
       </c>
       <c r="V103" s="22" t="n">
-        <v>2.483</v>
+        <v>37.633</v>
       </c>
       <c r="W103" s="22" t="n">
-        <v>15.047</v>
+        <v>189.989</v>
       </c>
       <c r="X103" s="22" t="n">
-        <v>6.52</v>
+        <v>40.315</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="20" t="inlineStr">
-        <is>
-          <t>고정자산 매각손실</t>
-        </is>
-      </c>
-      <c r="D104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="22" t="n">
-        <v>3.019</v>
-      </c>
-      <c r="U104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" s="22" t="n">
-        <v>0</v>
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="n">
+        <v>-323.236</v>
+      </c>
+      <c r="D104" s="12" t="n">
+        <v>-150.692</v>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>-489.989</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>436.742</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>100.892</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>327.795</v>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>-446.254</v>
+      </c>
+      <c r="J104" s="12" t="n">
+        <v>253.448</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>343.069</v>
+      </c>
+      <c r="L104" s="12" t="n">
+        <v>188.541</v>
+      </c>
+      <c r="M104" s="12" t="n">
+        <v>-56.738</v>
+      </c>
+      <c r="N104" s="12" t="n">
+        <v>412.858</v>
+      </c>
+      <c r="T104" s="12" t="n">
+        <v>1163.918</v>
+      </c>
+      <c r="U104" s="12" t="n">
+        <v>-787.593</v>
+      </c>
+      <c r="V104" s="12" t="n">
+        <v>-489.989</v>
+      </c>
+      <c r="W104" s="12" t="n">
+        <v>-446.254</v>
+      </c>
+      <c r="X104" s="12" t="n">
+        <v>-56.738</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="20" t="inlineStr">
-        <is>
-          <t>고정자산 제각손실</t>
-        </is>
-      </c>
-      <c r="C105" s="22" t="n">
-        <v>8.867000000000001</v>
-      </c>
-      <c r="D105" s="22" t="n">
-        <v>2.856</v>
-      </c>
-      <c r="E105" s="22" t="n">
-        <v>24.497</v>
-      </c>
-      <c r="F105" s="22" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="G105" s="22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H105" s="22" t="n">
-        <v>1.619</v>
-      </c>
-      <c r="I105" s="22" t="n">
-        <v>36.088</v>
-      </c>
-      <c r="J105" s="22" t="n">
-        <v>28.155</v>
-      </c>
-      <c r="K105" s="22" t="n">
-        <v>62.173</v>
-      </c>
-      <c r="L105" s="22" t="n">
-        <v>35.308</v>
-      </c>
-      <c r="M105" s="22" t="n">
-        <v>34.716</v>
-      </c>
-      <c r="N105" s="22" t="n">
-        <v>4.154</v>
-      </c>
-      <c r="T105" s="22" t="n">
-        <v>80.443</v>
-      </c>
-      <c r="U105" s="22" t="n">
-        <v>196.514</v>
-      </c>
-      <c r="V105" s="22" t="n">
-        <v>24.497</v>
-      </c>
-      <c r="W105" s="22" t="n">
-        <v>36.088</v>
-      </c>
-      <c r="X105" s="22" t="n">
-        <v>34.716</v>
+      <c r="A105" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G105" s="17">
+        <f>IF(OR(G104="",C104=""),"",IF(C104&lt;=0,"",IFERROR(G104/C104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H105" s="17">
+        <f>IF(OR(H104="",D104=""),"",IF(D104&lt;=0,"",IFERROR(H104/D104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I105" s="17">
+        <f>IF(OR(I104="",E104=""),"",IF(E104&lt;=0,"",IFERROR(I104/E104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J105" s="17">
+        <f>IF(OR(J104="",F104=""),"",IF(F104&lt;=0,"",IFERROR(J104/F104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K105" s="17">
+        <f>IF(OR(K104="",G104=""),"",IF(G104&lt;=0,"",IFERROR(K104/G104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L105" s="17">
+        <f>IF(OR(L104="",H104=""),"",IF(H104&lt;=0,"",IFERROR(L104/H104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M105" s="17">
+        <f>IF(OR(M104="",I104=""),"",IF(I104&lt;=0,"",IFERROR(M104/I104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N105" s="17">
+        <f>IF(OR(N104="",J104=""),"",IF(J104&lt;=0,"",IFERROR(N104/J104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T105" s="17">
+        <f>IF(OR(T104="",S104=""),"",IF(S104&lt;=0,"",IFERROR(T104/S104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U105" s="17">
+        <f>IF(OR(U104="",T104=""),"",IF(T104&lt;=0,"",IFERROR(U104/T104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V105" s="17">
+        <f>IF(OR(V104="",U104=""),"",IF(U104&lt;=0,"",IFERROR(V104/U104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W105" s="17">
+        <f>IF(OR(W104="",V104=""),"",IF(V104&lt;=0,"",IFERROR(W104/V104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X105" s="17">
+        <f>IF(OR(X104="",W104=""),"",IF(W104&lt;=0,"",IFERROR(X104/W104-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손실</t>
-        </is>
+          <t>고정자산 매각이익</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="n">
+        <v>52.689</v>
+      </c>
+      <c r="D106" s="22" t="n">
+        <v>7.671</v>
+      </c>
+      <c r="E106" s="22" t="n">
+        <v>2.483</v>
+      </c>
+      <c r="F106" s="22" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="G106" s="22" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H106" s="22" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="I106" s="22" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="J106" s="22" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="K106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="22" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="M106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="T106" s="22" t="n">
-        <v>-0.323</v>
+        <v>0.161</v>
       </c>
       <c r="U106" s="22" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="V106" s="22" t="n">
+        <v>2.483</v>
+      </c>
+      <c r="W106" s="22" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="X106" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20" t="inlineStr">
         <is>
-          <t>환경대책비</t>
-        </is>
-      </c>
-      <c r="C107" s="22" t="n">
-        <v>13.53</v>
+          <t>투자유가증권 매각이익</t>
+        </is>
       </c>
       <c r="D107" s="22" t="n">
-        <v>6.06</v>
+        <v>0.953</v>
       </c>
       <c r="E107" s="22" t="n">
         <v>0</v>
@@ -7306,611 +7455,503 @@
         <v>0</v>
       </c>
       <c r="I107" s="22" t="n">
+        <v>14.385</v>
+      </c>
+      <c r="U107" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="T107" s="22" t="n">
-        <v>38.55</v>
-      </c>
-      <c r="U107" s="22" t="n">
-        <v>50</v>
       </c>
       <c r="V107" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W107" s="22" t="n">
-        <v>0</v>
+        <v>14.385</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
+          <t>특별이익 합계</t>
         </is>
       </c>
       <c r="C108" s="22" t="n">
-        <v>43.69</v>
+        <v>52.777</v>
       </c>
       <c r="D108" s="22" t="n">
-        <v>8.917</v>
+        <v>8.622999999999999</v>
       </c>
       <c r="E108" s="22" t="n">
-        <v>3084.521</v>
+        <v>2.483</v>
       </c>
       <c r="F108" s="22" t="n">
-        <v>0.134</v>
+        <v>0.282</v>
       </c>
       <c r="G108" s="22" t="n">
-        <v>3.9</v>
+        <v>0.039</v>
       </c>
       <c r="H108" s="22" t="n">
-        <v>1.619</v>
+        <v>0.163</v>
       </c>
       <c r="I108" s="22" t="n">
-        <v>36.088</v>
+        <v>15.047</v>
       </c>
       <c r="J108" s="22" t="n">
-        <v>28.155</v>
+        <v>0.494</v>
       </c>
       <c r="K108" s="22" t="n">
-        <v>62.173</v>
+        <v>0</v>
       </c>
       <c r="L108" s="22" t="n">
-        <v>35.308</v>
+        <v>0.407</v>
       </c>
       <c r="M108" s="22" t="n">
-        <v>331.702</v>
+        <v>6.52</v>
       </c>
       <c r="N108" s="22" t="n">
-        <v>7.174</v>
+        <v>0</v>
       </c>
       <c r="T108" s="22" t="n">
-        <v>118.709</v>
+        <v>0.161</v>
       </c>
       <c r="U108" s="22" t="n">
-        <v>261.53</v>
+        <v>0.008</v>
       </c>
       <c r="V108" s="22" t="n">
-        <v>3084.521</v>
+        <v>2.483</v>
       </c>
       <c r="W108" s="22" t="n">
-        <v>36.088</v>
+        <v>15.047</v>
       </c>
       <c r="X108" s="22" t="n">
-        <v>331.702</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C109" s="12" t="n">
-        <v>-314.15</v>
-      </c>
-      <c r="D109" s="12" t="n">
-        <v>-150.985</v>
-      </c>
-      <c r="E109" s="12" t="n">
-        <v>-3572.027</v>
-      </c>
-      <c r="F109" s="12" t="n">
-        <v>436.89</v>
-      </c>
-      <c r="G109" s="12" t="n">
-        <v>97.03100000000001</v>
-      </c>
-      <c r="H109" s="12" t="n">
-        <v>326.34</v>
-      </c>
-      <c r="I109" s="12" t="n">
-        <v>-467.297</v>
-      </c>
-      <c r="J109" s="12" t="n">
-        <v>225.787</v>
-      </c>
-      <c r="K109" s="12" t="n">
-        <v>280.897</v>
-      </c>
-      <c r="L109" s="12" t="n">
-        <v>153.639</v>
-      </c>
-      <c r="M109" s="12" t="n">
-        <v>-381.919</v>
-      </c>
-      <c r="N109" s="12" t="n">
-        <v>405.684</v>
-      </c>
-      <c r="T109" s="12" t="n">
-        <v>1045.369</v>
-      </c>
-      <c r="U109" s="12" t="n">
-        <v>-1049.114</v>
-      </c>
-      <c r="V109" s="12" t="n">
-        <v>-3572.027</v>
-      </c>
-      <c r="W109" s="12" t="n">
-        <v>-467.297</v>
-      </c>
-      <c r="X109" s="12" t="n">
-        <v>-381.919</v>
+      <c r="A109" s="20" t="inlineStr">
+        <is>
+          <t>고정자산 매각손실</t>
+        </is>
+      </c>
+      <c r="D109" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="22" t="n">
+        <v>3.019</v>
+      </c>
+      <c r="U109" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
+          <t>고정자산 제각손실</t>
         </is>
       </c>
       <c r="C110" s="22" t="n">
-        <v>2.5</v>
+        <v>8.867000000000001</v>
       </c>
       <c r="D110" s="22" t="n">
-        <v>2.598</v>
+        <v>2.856</v>
       </c>
       <c r="E110" s="22" t="n">
-        <v>2.5</v>
+        <v>24.497</v>
       </c>
       <c r="F110" s="22" t="n">
-        <v>2.493</v>
+        <v>0.134</v>
       </c>
       <c r="G110" s="22" t="n">
-        <v>22.881</v>
+        <v>3.9</v>
       </c>
       <c r="H110" s="22" t="n">
-        <v>11.447</v>
+        <v>1.619</v>
       </c>
       <c r="I110" s="22" t="n">
-        <v>-0.836</v>
+        <v>36.088</v>
       </c>
       <c r="J110" s="22" t="n">
-        <v>5.797</v>
+        <v>28.155</v>
       </c>
       <c r="K110" s="22" t="n">
-        <v>55.608</v>
+        <v>62.173</v>
       </c>
       <c r="L110" s="22" t="n">
-        <v>-13.293</v>
+        <v>35.308</v>
       </c>
       <c r="M110" s="22" t="n">
-        <v>4.063</v>
+        <v>34.716</v>
       </c>
       <c r="N110" s="22" t="n">
-        <v>22.5</v>
+        <v>4.154</v>
       </c>
       <c r="T110" s="22" t="n">
-        <v>571.177</v>
+        <v>80.443</v>
       </c>
       <c r="U110" s="22" t="n">
-        <v>28.36</v>
+        <v>196.514</v>
       </c>
       <c r="V110" s="22" t="n">
-        <v>2.5</v>
+        <v>24.497</v>
       </c>
       <c r="W110" s="22" t="n">
-        <v>-0.836</v>
+        <v>36.088</v>
       </c>
       <c r="X110" s="22" t="n">
-        <v>4.063</v>
+        <v>34.716</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C111" s="22" t="n">
-        <v>-28.576</v>
-      </c>
-      <c r="D111" s="22" t="n">
-        <v>10.815</v>
-      </c>
-      <c r="E111" s="22" t="n">
-        <v>864.456</v>
-      </c>
-      <c r="F111" s="22" t="n">
-        <v>17.605</v>
-      </c>
-      <c r="G111" s="22" t="n">
-        <v>11.883</v>
-      </c>
-      <c r="H111" s="22" t="n">
-        <v>12.628</v>
-      </c>
-      <c r="I111" s="22" t="n">
-        <v>136.817</v>
-      </c>
-      <c r="J111" s="22" t="n">
-        <v>16.566</v>
-      </c>
-      <c r="K111" s="22" t="n">
-        <v>14.618</v>
-      </c>
-      <c r="L111" s="22" t="n">
-        <v>31.248</v>
-      </c>
-      <c r="M111" s="22" t="n">
-        <v>93.667</v>
-      </c>
-      <c r="N111" s="22" t="n">
-        <v>18.684</v>
+          <t>투자유가증권 평가손실</t>
+        </is>
       </c>
       <c r="T111" s="22" t="n">
-        <v>-280.721</v>
+        <v>-0.323</v>
       </c>
       <c r="U111" s="22" t="n">
-        <v>-210.817</v>
-      </c>
-      <c r="V111" s="22" t="n">
-        <v>864.456</v>
-      </c>
-      <c r="W111" s="22" t="n">
-        <v>136.817</v>
-      </c>
-      <c r="X111" s="22" t="n">
-        <v>93.667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
+          <t>환경대책비</t>
         </is>
       </c>
       <c r="C112" s="22" t="n">
-        <v>-26.077</v>
+        <v>13.53</v>
       </c>
       <c r="D112" s="22" t="n">
-        <v>13.414</v>
+        <v>6.06</v>
       </c>
       <c r="E112" s="22" t="n">
-        <v>866.956</v>
-      </c>
-      <c r="F112" s="22" t="n">
-        <v>20.099</v>
-      </c>
-      <c r="G112" s="22" t="n">
-        <v>34.764</v>
+        <v>0</v>
       </c>
       <c r="H112" s="22" t="n">
-        <v>24.074</v>
+        <v>0</v>
       </c>
       <c r="I112" s="22" t="n">
-        <v>135.982</v>
-      </c>
-      <c r="J112" s="22" t="n">
-        <v>22.364</v>
-      </c>
-      <c r="K112" s="22" t="n">
-        <v>70.22499999999999</v>
-      </c>
-      <c r="L112" s="22" t="n">
-        <v>17.955</v>
-      </c>
-      <c r="M112" s="22" t="n">
-        <v>97.73</v>
-      </c>
-      <c r="N112" s="22" t="n">
-        <v>41.184</v>
+        <v>0</v>
       </c>
       <c r="T112" s="22" t="n">
-        <v>290.455</v>
+        <v>38.55</v>
       </c>
       <c r="U112" s="22" t="n">
-        <v>-182.457</v>
+        <v>50</v>
       </c>
       <c r="V112" s="22" t="n">
-        <v>866.956</v>
+        <v>0</v>
       </c>
       <c r="W112" s="22" t="n">
-        <v>135.982</v>
-      </c>
-      <c r="X112" s="22" t="n">
-        <v>97.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C113" s="12" t="n">
-        <v>-288.073</v>
-      </c>
-      <c r="D113" s="12" t="n">
-        <v>-164.4</v>
-      </c>
-      <c r="E113" s="12" t="n">
-        <v>-4438.983</v>
-      </c>
-      <c r="F113" s="12" t="n">
-        <v>416.79</v>
-      </c>
-      <c r="G113" s="12" t="n">
-        <v>62.268</v>
-      </c>
-      <c r="H113" s="12" t="n">
-        <v>302.265</v>
-      </c>
-      <c r="I113" s="12" t="n">
-        <v>-603.278</v>
-      </c>
-      <c r="J113" s="12" t="n">
-        <v>203.423</v>
-      </c>
-      <c r="K113" s="12" t="n">
-        <v>210.671</v>
-      </c>
-      <c r="L113" s="12" t="n">
-        <v>135.684</v>
-      </c>
-      <c r="M113" s="12" t="n">
-        <v>-479.649</v>
-      </c>
-      <c r="N113" s="12" t="n">
-        <v>364.499</v>
-      </c>
-      <c r="T113" s="12" t="n">
-        <v>754.915</v>
-      </c>
-      <c r="U113" s="12" t="n">
-        <v>-866.657</v>
-      </c>
-      <c r="V113" s="12" t="n">
-        <v>-4438.983</v>
-      </c>
-      <c r="W113" s="12" t="n">
-        <v>-603.278</v>
-      </c>
-      <c r="X113" s="12" t="n">
-        <v>-479.649</v>
+      <c r="A113" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="C113" s="22" t="n">
+        <v>43.69</v>
+      </c>
+      <c r="D113" s="22" t="n">
+        <v>8.917</v>
+      </c>
+      <c r="E113" s="22" t="n">
+        <v>3084.521</v>
+      </c>
+      <c r="F113" s="22" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="G113" s="22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H113" s="22" t="n">
+        <v>1.619</v>
+      </c>
+      <c r="I113" s="22" t="n">
+        <v>36.088</v>
+      </c>
+      <c r="J113" s="22" t="n">
+        <v>28.155</v>
+      </c>
+      <c r="K113" s="22" t="n">
+        <v>62.173</v>
+      </c>
+      <c r="L113" s="22" t="n">
+        <v>35.308</v>
+      </c>
+      <c r="M113" s="22" t="n">
+        <v>331.702</v>
+      </c>
+      <c r="N113" s="22" t="n">
+        <v>7.174</v>
+      </c>
+      <c r="T113" s="22" t="n">
+        <v>118.709</v>
+      </c>
+      <c r="U113" s="22" t="n">
+        <v>261.53</v>
+      </c>
+      <c r="V113" s="22" t="n">
+        <v>3084.521</v>
+      </c>
+      <c r="W113" s="22" t="n">
+        <v>36.088</v>
+      </c>
+      <c r="X113" s="22" t="n">
+        <v>331.702</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>지배주주 순이익</t>
+          <t>법인세차감전 순이익</t>
         </is>
       </c>
       <c r="C114" s="12" t="n">
-        <v>-288.073</v>
+        <v>-314.15</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>-164.4</v>
+        <v>-150.985</v>
       </c>
       <c r="E114" s="12" t="n">
-        <v>-4438.983</v>
+        <v>-3572.027</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>416.79</v>
+        <v>436.89</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>62.268</v>
+        <v>97.03100000000001</v>
       </c>
       <c r="H114" s="12" t="n">
-        <v>302.265</v>
+        <v>326.34</v>
       </c>
       <c r="I114" s="12" t="n">
-        <v>-603.278</v>
+        <v>-467.297</v>
       </c>
       <c r="J114" s="12" t="n">
-        <v>203.423</v>
+        <v>225.787</v>
       </c>
       <c r="K114" s="12" t="n">
-        <v>210.671</v>
+        <v>280.897</v>
       </c>
       <c r="L114" s="12" t="n">
-        <v>135.684</v>
+        <v>153.639</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>-479.649</v>
+        <v>-381.919</v>
       </c>
       <c r="N114" s="12" t="n">
-        <v>364.499</v>
+        <v>405.684</v>
       </c>
       <c r="T114" s="12" t="n">
-        <v>754.915</v>
+        <v>1045.369</v>
       </c>
       <c r="U114" s="12" t="n">
-        <v>-866.657</v>
+        <v>-1049.114</v>
       </c>
       <c r="V114" s="12" t="n">
-        <v>-4438.983</v>
+        <v>-3572.027</v>
       </c>
       <c r="W114" s="12" t="n">
-        <v>-603.278</v>
+        <v>-467.297</v>
       </c>
       <c r="X114" s="12" t="n">
-        <v>-479.649</v>
+        <v>-381.919</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C115" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D115" s="22" t="n">
+        <v>2.598</v>
+      </c>
+      <c r="E115" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F115" s="22" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="G115" s="22" t="n">
+        <v>22.881</v>
+      </c>
+      <c r="H115" s="22" t="n">
+        <v>11.447</v>
+      </c>
+      <c r="I115" s="22" t="n">
+        <v>-0.836</v>
+      </c>
+      <c r="J115" s="22" t="n">
+        <v>5.797</v>
+      </c>
+      <c r="K115" s="22" t="n">
+        <v>55.608</v>
+      </c>
+      <c r="L115" s="22" t="n">
+        <v>-13.293</v>
+      </c>
+      <c r="M115" s="22" t="n">
+        <v>4.063</v>
+      </c>
+      <c r="N115" s="22" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="T115" s="22" t="n">
+        <v>571.177</v>
+      </c>
+      <c r="U115" s="22" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="V115" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W115" s="22" t="n">
+        <v>-0.836</v>
+      </c>
+      <c r="X115" s="22" t="n">
+        <v>4.063</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="18" t="inlineStr">
-        <is>
-          <t>포괄손익 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B116" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 3개월 단독</t>
-        </is>
-      </c>
-      <c r="C116" s="18" t="n"/>
-      <c r="D116" s="18" t="n"/>
-      <c r="E116" s="18" t="n"/>
-      <c r="F116" s="18" t="n"/>
-      <c r="G116" s="18" t="n"/>
-      <c r="H116" s="18" t="n"/>
-      <c r="I116" s="18" t="n"/>
-      <c r="J116" s="18" t="n"/>
-      <c r="K116" s="18" t="n"/>
-      <c r="L116" s="18" t="n"/>
-      <c r="M116" s="18" t="n"/>
-      <c r="N116" s="18" t="n"/>
-      <c r="O116" s="18" t="n"/>
-      <c r="P116" s="18" t="n"/>
-      <c r="Q116" s="18" t="n"/>
-      <c r="R116" s="18" t="n"/>
-      <c r="S116" s="18" t="n"/>
-      <c r="T116" s="18" t="n"/>
-      <c r="U116" s="18" t="n"/>
-      <c r="V116" s="18" t="n"/>
-      <c r="W116" s="18" t="n"/>
-      <c r="X116" s="18" t="n"/>
-      <c r="Y116" s="18" t="n"/>
-      <c r="Z116" s="18" t="n"/>
-      <c r="AA116" s="18" t="n"/>
-      <c r="AB116" s="18" t="n"/>
-      <c r="AC116" s="18" t="n"/>
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C116" s="22" t="n">
+        <v>-28.576</v>
+      </c>
+      <c r="D116" s="22" t="n">
+        <v>10.815</v>
+      </c>
+      <c r="E116" s="22" t="n">
+        <v>864.456</v>
+      </c>
+      <c r="F116" s="22" t="n">
+        <v>17.605</v>
+      </c>
+      <c r="G116" s="22" t="n">
+        <v>11.883</v>
+      </c>
+      <c r="H116" s="22" t="n">
+        <v>12.628</v>
+      </c>
+      <c r="I116" s="22" t="n">
+        <v>136.817</v>
+      </c>
+      <c r="J116" s="22" t="n">
+        <v>16.566</v>
+      </c>
+      <c r="K116" s="22" t="n">
+        <v>14.618</v>
+      </c>
+      <c r="L116" s="22" t="n">
+        <v>31.248</v>
+      </c>
+      <c r="M116" s="22" t="n">
+        <v>93.667</v>
+      </c>
+      <c r="N116" s="22" t="n">
+        <v>18.684</v>
+      </c>
+      <c r="T116" s="22" t="n">
+        <v>-280.721</v>
+      </c>
+      <c r="U116" s="22" t="n">
+        <v>-210.817</v>
+      </c>
+      <c r="V116" s="22" t="n">
+        <v>864.456</v>
+      </c>
+      <c r="W116" s="22" t="n">
+        <v>136.817</v>
+      </c>
+      <c r="X116" s="22" t="n">
+        <v>93.667</v>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H117" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I117" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J117" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K117" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L117" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M117" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N117" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O117" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P117" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q117" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R117" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S117" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T117" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U117" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V117" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W117" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X117" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y117" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z117" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA117" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB117" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC117" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A117" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C117" s="22" t="n">
+        <v>-26.077</v>
+      </c>
+      <c r="D117" s="22" t="n">
+        <v>13.414</v>
+      </c>
+      <c r="E117" s="22" t="n">
+        <v>866.956</v>
+      </c>
+      <c r="F117" s="22" t="n">
+        <v>20.099</v>
+      </c>
+      <c r="G117" s="22" t="n">
+        <v>34.764</v>
+      </c>
+      <c r="H117" s="22" t="n">
+        <v>24.074</v>
+      </c>
+      <c r="I117" s="22" t="n">
+        <v>135.982</v>
+      </c>
+      <c r="J117" s="22" t="n">
+        <v>22.364</v>
+      </c>
+      <c r="K117" s="22" t="n">
+        <v>70.22499999999999</v>
+      </c>
+      <c r="L117" s="22" t="n">
+        <v>17.955</v>
+      </c>
+      <c r="M117" s="22" t="n">
+        <v>97.73</v>
+      </c>
+      <c r="N117" s="22" t="n">
+        <v>41.184</v>
+      </c>
+      <c r="T117" s="22" t="n">
+        <v>290.455</v>
+      </c>
+      <c r="U117" s="22" t="n">
+        <v>-182.457</v>
+      </c>
+      <c r="V117" s="22" t="n">
+        <v>866.956</v>
+      </c>
+      <c r="W117" s="22" t="n">
+        <v>135.982</v>
+      </c>
+      <c r="X117" s="22" t="n">
+        <v>97.73</v>
       </c>
     </row>
     <row r="118">
@@ -7972,2887 +8013,3317 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="20" t="inlineStr">
+      <c r="A119" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G119" s="17">
+        <f>IF(OR(G118="",C118=""),"",IF(C118&lt;=0,"",IFERROR(G118/C118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H119" s="17">
+        <f>IF(OR(H118="",D118=""),"",IF(D118&lt;=0,"",IFERROR(H118/D118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I119" s="17">
+        <f>IF(OR(I118="",E118=""),"",IF(E118&lt;=0,"",IFERROR(I118/E118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J119" s="17">
+        <f>IF(OR(J118="",F118=""),"",IF(F118&lt;=0,"",IFERROR(J118/F118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K119" s="17">
+        <f>IF(OR(K118="",G118=""),"",IF(G118&lt;=0,"",IFERROR(K118/G118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L119" s="17">
+        <f>IF(OR(L118="",H118=""),"",IF(H118&lt;=0,"",IFERROR(L118/H118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M119" s="17">
+        <f>IF(OR(M118="",I118=""),"",IF(I118&lt;=0,"",IFERROR(M118/I118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N119" s="17">
+        <f>IF(OR(N118="",J118=""),"",IF(J118&lt;=0,"",IFERROR(N118/J118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T119" s="17">
+        <f>IF(OR(T118="",S118=""),"",IF(S118&lt;=0,"",IFERROR(T118/S118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U119" s="17">
+        <f>IF(OR(U118="",T118=""),"",IF(T118&lt;=0,"",IFERROR(U118/T118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V119" s="17">
+        <f>IF(OR(V118="",U118=""),"",IF(U118&lt;=0,"",IFERROR(V118/U118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W119" s="17">
+        <f>IF(OR(W118="",V118=""),"",IF(V118&lt;=0,"",IFERROR(W118/V118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X119" s="17">
+        <f>IF(OR(X118="",W118=""),"",IF(W118&lt;=0,"",IFERROR(X118/W118-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 순이익</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="n">
+        <v>-288.073</v>
+      </c>
+      <c r="D120" s="12" t="n">
+        <v>-164.4</v>
+      </c>
+      <c r="E120" s="12" t="n">
+        <v>-4438.983</v>
+      </c>
+      <c r="F120" s="12" t="n">
+        <v>416.79</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>62.268</v>
+      </c>
+      <c r="H120" s="12" t="n">
+        <v>302.265</v>
+      </c>
+      <c r="I120" s="12" t="n">
+        <v>-603.278</v>
+      </c>
+      <c r="J120" s="12" t="n">
+        <v>203.423</v>
+      </c>
+      <c r="K120" s="12" t="n">
+        <v>210.671</v>
+      </c>
+      <c r="L120" s="12" t="n">
+        <v>135.684</v>
+      </c>
+      <c r="M120" s="12" t="n">
+        <v>-479.649</v>
+      </c>
+      <c r="N120" s="12" t="n">
+        <v>364.499</v>
+      </c>
+      <c r="T120" s="12" t="n">
+        <v>754.915</v>
+      </c>
+      <c r="U120" s="12" t="n">
+        <v>-866.657</v>
+      </c>
+      <c r="V120" s="12" t="n">
+        <v>-4438.983</v>
+      </c>
+      <c r="W120" s="12" t="n">
+        <v>-603.278</v>
+      </c>
+      <c r="X120" s="12" t="n">
+        <v>-479.649</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G121" s="17">
+        <f>IF(OR(G120="",C120=""),"",IF(C120&lt;=0,"",IFERROR(G120/C120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H121" s="17">
+        <f>IF(OR(H120="",D120=""),"",IF(D120&lt;=0,"",IFERROR(H120/D120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I121" s="17">
+        <f>IF(OR(I120="",E120=""),"",IF(E120&lt;=0,"",IFERROR(I120/E120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J121" s="17">
+        <f>IF(OR(J120="",F120=""),"",IF(F120&lt;=0,"",IFERROR(J120/F120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K121" s="17">
+        <f>IF(OR(K120="",G120=""),"",IF(G120&lt;=0,"",IFERROR(K120/G120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L121" s="17">
+        <f>IF(OR(L120="",H120=""),"",IF(H120&lt;=0,"",IFERROR(L120/H120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M121" s="17">
+        <f>IF(OR(M120="",I120=""),"",IF(I120&lt;=0,"",IFERROR(M120/I120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N121" s="17">
+        <f>IF(OR(N120="",J120=""),"",IF(J120&lt;=0,"",IFERROR(N120/J120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T121" s="17">
+        <f>IF(OR(T120="",S120=""),"",IF(S120&lt;=0,"",IFERROR(T120/S120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U121" s="17">
+        <f>IF(OR(U120="",T120=""),"",IF(T120&lt;=0,"",IFERROR(U120/T120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V121" s="17">
+        <f>IF(OR(V120="",U120=""),"",IF(U120&lt;=0,"",IFERROR(V120/U120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W121" s="17">
+        <f>IF(OR(W120="",V120=""),"",IF(V120&lt;=0,"",IFERROR(W120/V120-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X121" s="17">
+        <f>IF(OR(X120="",W120=""),"",IF(W120&lt;=0,"",IFERROR(X120/W120-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="18" t="inlineStr">
+        <is>
+          <t>포괄손익 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B123" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 3개월 단독</t>
+        </is>
+      </c>
+      <c r="C123" s="18" t="n"/>
+      <c r="D123" s="18" t="n"/>
+      <c r="E123" s="18" t="n"/>
+      <c r="F123" s="18" t="n"/>
+      <c r="G123" s="18" t="n"/>
+      <c r="H123" s="18" t="n"/>
+      <c r="I123" s="18" t="n"/>
+      <c r="J123" s="18" t="n"/>
+      <c r="K123" s="18" t="n"/>
+      <c r="L123" s="18" t="n"/>
+      <c r="M123" s="18" t="n"/>
+      <c r="N123" s="18" t="n"/>
+      <c r="O123" s="18" t="n"/>
+      <c r="P123" s="18" t="n"/>
+      <c r="Q123" s="18" t="n"/>
+      <c r="R123" s="18" t="n"/>
+      <c r="S123" s="18" t="n"/>
+      <c r="T123" s="18" t="n"/>
+      <c r="U123" s="18" t="n"/>
+      <c r="V123" s="18" t="n"/>
+      <c r="W123" s="18" t="n"/>
+      <c r="X123" s="18" t="n"/>
+      <c r="Y123" s="18" t="n"/>
+      <c r="Z123" s="18" t="n"/>
+      <c r="AA123" s="18" t="n"/>
+      <c r="AB123" s="18" t="n"/>
+      <c r="AC123" s="18" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M124" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N124" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O124" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P124" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q124" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R124" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S124" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T124" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U124" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V124" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W124" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X124" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y124" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z124" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA124" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB124" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC124" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="n">
+        <v>-288.073</v>
+      </c>
+      <c r="D125" s="12" t="n">
+        <v>-164.4</v>
+      </c>
+      <c r="E125" s="12" t="n">
+        <v>-4438.983</v>
+      </c>
+      <c r="F125" s="12" t="n">
+        <v>416.79</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>62.268</v>
+      </c>
+      <c r="H125" s="12" t="n">
+        <v>302.265</v>
+      </c>
+      <c r="I125" s="12" t="n">
+        <v>-603.278</v>
+      </c>
+      <c r="J125" s="12" t="n">
+        <v>203.423</v>
+      </c>
+      <c r="K125" s="12" t="n">
+        <v>210.671</v>
+      </c>
+      <c r="L125" s="12" t="n">
+        <v>135.684</v>
+      </c>
+      <c r="M125" s="12" t="n">
+        <v>-479.649</v>
+      </c>
+      <c r="N125" s="12" t="n">
+        <v>364.499</v>
+      </c>
+      <c r="T125" s="12" t="n">
+        <v>754.915</v>
+      </c>
+      <c r="U125" s="12" t="n">
+        <v>-866.657</v>
+      </c>
+      <c r="V125" s="12" t="n">
+        <v>-4438.983</v>
+      </c>
+      <c r="W125" s="12" t="n">
+        <v>-603.278</v>
+      </c>
+      <c r="X125" s="12" t="n">
+        <v>-479.649</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="20" t="inlineStr">
         <is>
           <t>기타유가증권 평가차액</t>
         </is>
       </c>
-      <c r="C119" s="22" t="n">
+      <c r="C126" s="22" t="n">
         <v>3.039</v>
       </c>
-      <c r="D119" s="22" t="n">
+      <c r="D126" s="22" t="n">
         <v>-36.423</v>
       </c>
-      <c r="E119" s="22" t="n">
+      <c r="E126" s="22" t="n">
         <v>61.816</v>
       </c>
-      <c r="F119" s="22" t="n">
+      <c r="F126" s="22" t="n">
         <v>26.408</v>
       </c>
-      <c r="G119" s="22" t="n">
+      <c r="G126" s="22" t="n">
         <v>-61.084</v>
       </c>
-      <c r="H119" s="22" t="n">
+      <c r="H126" s="22" t="n">
         <v>30.766</v>
       </c>
-      <c r="I119" s="22" t="n">
+      <c r="I126" s="22" t="n">
         <v>-0.794</v>
       </c>
-      <c r="J119" s="22" t="n">
+      <c r="J126" s="22" t="n">
         <v>11.503</v>
       </c>
-      <c r="K119" s="22" t="n">
+      <c r="K126" s="22" t="n">
         <v>84.869</v>
       </c>
-      <c r="L119" s="22" t="n">
+      <c r="L126" s="22" t="n">
         <v>19.431</v>
       </c>
-      <c r="M119" s="22" t="n">
+      <c r="M126" s="22" t="n">
         <v>9.877000000000001</v>
       </c>
-      <c r="N119" s="22" t="n">
+      <c r="N126" s="22" t="n">
         <v>191.849</v>
       </c>
-      <c r="T119" s="22" t="n">
+      <c r="T126" s="22" t="n">
         <v>-52.666</v>
       </c>
-      <c r="U119" s="22" t="n">
+      <c r="U126" s="22" t="n">
         <v>1.197</v>
       </c>
-      <c r="V119" s="22" t="n">
+      <c r="V126" s="22" t="n">
         <v>61.816</v>
       </c>
-      <c r="W119" s="22" t="n">
+      <c r="W126" s="22" t="n">
         <v>-0.794</v>
       </c>
-      <c r="X119" s="22" t="n">
+      <c r="X126" s="22" t="n">
         <v>9.877000000000001</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="20" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="20" t="inlineStr">
         <is>
           <t>퇴직급여 조정액</t>
         </is>
       </c>
-      <c r="C120" s="22" t="n">
+      <c r="C127" s="22" t="n">
         <v>0.067</v>
       </c>
-      <c r="D120" s="22" t="n">
+      <c r="D127" s="22" t="n">
         <v>0.067</v>
       </c>
-      <c r="E120" s="22" t="n">
+      <c r="E127" s="22" t="n">
         <v>400.615</v>
       </c>
-      <c r="F120" s="22" t="n">
+      <c r="F127" s="22" t="n">
         <v>-17.983</v>
       </c>
-      <c r="G120" s="22" t="n">
+      <c r="G127" s="22" t="n">
         <v>-17.984</v>
       </c>
-      <c r="H120" s="22" t="n">
+      <c r="H127" s="22" t="n">
         <v>-17.984</v>
       </c>
-      <c r="I120" s="22" t="n">
+      <c r="I127" s="22" t="n">
         <v>239.63</v>
       </c>
-      <c r="J120" s="22" t="n">
+      <c r="J127" s="22" t="n">
         <v>-15.996</v>
       </c>
-      <c r="K120" s="22" t="n">
+      <c r="K127" s="22" t="n">
         <v>-15.996</v>
       </c>
-      <c r="L120" s="22" t="n">
+      <c r="L127" s="22" t="n">
         <v>-15.996</v>
       </c>
-      <c r="M120" s="22" t="n">
+      <c r="M127" s="22" t="n">
         <v>786.6130000000001</v>
       </c>
-      <c r="N120" s="22" t="n">
+      <c r="N127" s="22" t="n">
         <v>-32.098</v>
       </c>
-      <c r="T120" s="22" t="n">
+      <c r="T127" s="22" t="n">
         <v>-180.17</v>
       </c>
-      <c r="U120" s="22" t="n">
+      <c r="U127" s="22" t="n">
         <v>225.958</v>
       </c>
-      <c r="V120" s="22" t="n">
+      <c r="V127" s="22" t="n">
         <v>400.615</v>
       </c>
-      <c r="W120" s="22" t="n">
+      <c r="W127" s="22" t="n">
         <v>239.63</v>
       </c>
-      <c r="X120" s="22" t="n">
+      <c r="X127" s="22" t="n">
         <v>786.6130000000001</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="20" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
         <is>
           <t>기타포괄손익 합계</t>
         </is>
       </c>
-      <c r="C121" s="22" t="n">
+      <c r="C128" s="22" t="n">
         <v>3.105</v>
       </c>
-      <c r="D121" s="22" t="n">
+      <c r="D128" s="22" t="n">
         <v>-36.356</v>
       </c>
-      <c r="E121" s="22" t="n">
+      <c r="E128" s="22" t="n">
         <v>462.431</v>
       </c>
-      <c r="F121" s="22" t="n">
+      <c r="F128" s="22" t="n">
         <v>8.423999999999999</v>
       </c>
-      <c r="G121" s="22" t="n">
+      <c r="G128" s="22" t="n">
         <v>-79.068</v>
       </c>
-      <c r="H121" s="22" t="n">
+      <c r="H128" s="22" t="n">
         <v>12.783</v>
       </c>
-      <c r="I121" s="22" t="n">
+      <c r="I128" s="22" t="n">
         <v>238.835</v>
       </c>
-      <c r="J121" s="22" t="n">
+      <c r="J128" s="22" t="n">
         <v>-4.492</v>
       </c>
-      <c r="K121" s="22" t="n">
+      <c r="K128" s="22" t="n">
         <v>68.872</v>
       </c>
-      <c r="L121" s="22" t="n">
+      <c r="L128" s="22" t="n">
         <v>3.435</v>
       </c>
-      <c r="M121" s="22" t="n">
+      <c r="M128" s="22" t="n">
         <v>796.491</v>
       </c>
-      <c r="N121" s="22" t="n">
+      <c r="N128" s="22" t="n">
         <v>159.751</v>
       </c>
-      <c r="T121" s="22" t="n">
+      <c r="T128" s="22" t="n">
         <v>-232.836</v>
       </c>
-      <c r="U121" s="22" t="n">
+      <c r="U128" s="22" t="n">
         <v>227.155</v>
       </c>
-      <c r="V121" s="22" t="n">
+      <c r="V128" s="22" t="n">
         <v>462.431</v>
       </c>
-      <c r="W121" s="22" t="n">
+      <c r="W128" s="22" t="n">
         <v>238.835</v>
       </c>
-      <c r="X121" s="22" t="n">
+      <c r="X128" s="22" t="n">
         <v>796.491</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="9" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>포괄이익</t>
         </is>
       </c>
-      <c r="C122" s="12" t="n">
+      <c r="C129" s="12" t="n">
         <v>-284.968</v>
       </c>
-      <c r="D122" s="12" t="n">
+      <c r="D129" s="12" t="n">
         <v>-200.755</v>
       </c>
-      <c r="E122" s="12" t="n">
+      <c r="E129" s="12" t="n">
         <v>-3976.552</v>
       </c>
-      <c r="F122" s="12" t="n">
+      <c r="F129" s="12" t="n">
         <v>425.215</v>
       </c>
-      <c r="G122" s="12" t="n">
+      <c r="G129" s="12" t="n">
         <v>-16.801</v>
       </c>
-      <c r="H122" s="12" t="n">
+      <c r="H129" s="12" t="n">
         <v>315.048</v>
       </c>
-      <c r="I122" s="12" t="n">
+      <c r="I129" s="12" t="n">
         <v>-364.443</v>
       </c>
-      <c r="J122" s="12" t="n">
+      <c r="J129" s="12" t="n">
         <v>198.93</v>
       </c>
-      <c r="K122" s="12" t="n">
+      <c r="K129" s="12" t="n">
         <v>279.545</v>
       </c>
-      <c r="L122" s="12" t="n">
+      <c r="L129" s="12" t="n">
         <v>139.118</v>
       </c>
-      <c r="M122" s="12" t="n">
+      <c r="M129" s="12" t="n">
         <v>316.842</v>
       </c>
-      <c r="N122" s="12" t="n">
+      <c r="N129" s="12" t="n">
         <v>524.25</v>
       </c>
-      <c r="T122" s="12" t="n">
+      <c r="T129" s="12" t="n">
         <v>522.078</v>
       </c>
-      <c r="U122" s="12" t="n">
+      <c r="U129" s="12" t="n">
         <v>-639.503</v>
       </c>
-      <c r="V122" s="12" t="n">
+      <c r="V129" s="12" t="n">
         <v>-3976.552</v>
       </c>
-      <c r="W122" s="12" t="n">
+      <c r="W129" s="12" t="n">
         <v>-364.443</v>
       </c>
-      <c r="X122" s="12" t="n">
+      <c r="X129" s="12" t="n">
         <v>316.842</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="9" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
         <is>
           <t>지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C123" s="12" t="n">
+      <c r="C130" s="12" t="n">
         <v>-284.968</v>
       </c>
-      <c r="D123" s="12" t="n">
+      <c r="D130" s="12" t="n">
         <v>-200.755</v>
       </c>
-      <c r="E123" s="12" t="n">
+      <c r="E130" s="12" t="n">
         <v>-3976.552</v>
       </c>
-      <c r="F123" s="12" t="n">
+      <c r="F130" s="12" t="n">
         <v>425.215</v>
       </c>
-      <c r="G123" s="12" t="n">
+      <c r="G130" s="12" t="n">
         <v>-16.801</v>
       </c>
-      <c r="H123" s="12" t="n">
+      <c r="H130" s="12" t="n">
         <v>315.048</v>
       </c>
-      <c r="I123" s="12" t="n">
+      <c r="I130" s="12" t="n">
         <v>-364.443</v>
       </c>
-      <c r="J123" s="12" t="n">
+      <c r="J130" s="12" t="n">
         <v>198.93</v>
       </c>
-      <c r="K123" s="12" t="n">
+      <c r="K130" s="12" t="n">
         <v>279.545</v>
       </c>
-      <c r="L123" s="12" t="n">
+      <c r="L130" s="12" t="n">
         <v>139.118</v>
       </c>
-      <c r="M123" s="12" t="n">
+      <c r="M130" s="12" t="n">
         <v>316.842</v>
       </c>
-      <c r="N123" s="12" t="n">
+      <c r="N130" s="12" t="n">
         <v>524.25</v>
       </c>
-      <c r="T123" s="12" t="n">
+      <c r="T130" s="12" t="n">
         <v>522.078</v>
       </c>
-      <c r="U123" s="12" t="n">
+      <c r="U130" s="12" t="n">
         <v>-639.503</v>
       </c>
-      <c r="V123" s="12" t="n">
+      <c r="V130" s="12" t="n">
         <v>-3976.552</v>
       </c>
-      <c r="W123" s="12" t="n">
+      <c r="W130" s="12" t="n">
         <v>-364.443</v>
       </c>
-      <c r="X123" s="12" t="n">
+      <c r="X130" s="12" t="n">
         <v>316.842</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="9" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
         <is>
           <t>비지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C124" s="12" t="n">
+      <c r="C131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="12" t="n">
+      <c r="D131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E124" s="12" t="n">
+      <c r="E131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F124" s="12" t="n">
+      <c r="F131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G124" s="12" t="n">
+      <c r="G131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H124" s="12" t="n">
+      <c r="H131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I124" s="12" t="n">
+      <c r="I131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J124" s="12" t="n">
+      <c r="J131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K124" s="12" t="n">
+      <c r="K131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L124" s="12" t="n">
+      <c r="L131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M124" s="12" t="n">
+      <c r="M131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N124" s="12" t="n">
+      <c r="N131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="T124" s="12" t="n">
+      <c r="T131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="U124" s="12" t="n">
+      <c r="U131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="12" t="n">
+      <c r="V131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="W124" s="12" t="n">
+      <c r="W131" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="X124" s="12" t="n">
+      <c r="X131" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="18" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B126" s="44" t="inlineStr">
+      <c r="B133" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C126" s="18" t="n"/>
-      <c r="D126" s="18" t="n"/>
-      <c r="E126" s="18" t="n"/>
-      <c r="F126" s="18" t="n"/>
-      <c r="G126" s="18" t="n"/>
-      <c r="H126" s="18" t="n"/>
-      <c r="I126" s="18" t="n"/>
-      <c r="J126" s="18" t="n"/>
-      <c r="K126" s="18" t="n"/>
-      <c r="L126" s="18" t="n"/>
-      <c r="M126" s="18" t="n"/>
-      <c r="N126" s="18" t="n"/>
-      <c r="O126" s="18" t="n"/>
-      <c r="P126" s="18" t="n"/>
-      <c r="Q126" s="18" t="n"/>
-      <c r="R126" s="18" t="n"/>
-      <c r="S126" s="18" t="n"/>
-      <c r="T126" s="18" t="n"/>
-      <c r="U126" s="18" t="n"/>
-      <c r="V126" s="18" t="n"/>
-      <c r="W126" s="18" t="n"/>
-      <c r="X126" s="18" t="n"/>
-      <c r="Y126" s="18" t="n"/>
-      <c r="Z126" s="18" t="n"/>
-      <c r="AA126" s="18" t="n"/>
-      <c r="AB126" s="18" t="n"/>
-      <c r="AC126" s="18" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr">
+      <c r="C133" s="18" t="n"/>
+      <c r="D133" s="18" t="n"/>
+      <c r="E133" s="18" t="n"/>
+      <c r="F133" s="18" t="n"/>
+      <c r="G133" s="18" t="n"/>
+      <c r="H133" s="18" t="n"/>
+      <c r="I133" s="18" t="n"/>
+      <c r="J133" s="18" t="n"/>
+      <c r="K133" s="18" t="n"/>
+      <c r="L133" s="18" t="n"/>
+      <c r="M133" s="18" t="n"/>
+      <c r="N133" s="18" t="n"/>
+      <c r="O133" s="18" t="n"/>
+      <c r="P133" s="18" t="n"/>
+      <c r="Q133" s="18" t="n"/>
+      <c r="R133" s="18" t="n"/>
+      <c r="S133" s="18" t="n"/>
+      <c r="T133" s="18" t="n"/>
+      <c r="U133" s="18" t="n"/>
+      <c r="V133" s="18" t="n"/>
+      <c r="W133" s="18" t="n"/>
+      <c r="X133" s="18" t="n"/>
+      <c r="Y133" s="18" t="n"/>
+      <c r="Z133" s="18" t="n"/>
+      <c r="AA133" s="18" t="n"/>
+      <c r="AB133" s="18" t="n"/>
+      <c r="AC133" s="18" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B127" s="5" t="inlineStr">
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C127" s="5" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E127" s="5" t="inlineStr">
+      <c r="E134" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
+      <c r="F134" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G127" s="5" t="inlineStr">
+      <c r="G134" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H127" s="5" t="inlineStr">
+      <c r="H134" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I127" s="5" t="inlineStr">
+      <c r="I134" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J127" s="5" t="inlineStr">
+      <c r="J134" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K127" s="5" t="inlineStr">
+      <c r="K134" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L127" s="5" t="inlineStr">
+      <c r="L134" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M127" s="5" t="inlineStr">
+      <c r="M134" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N127" s="5" t="inlineStr">
+      <c r="N134" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O127" s="5" t="inlineStr">
+      <c r="O134" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P127" s="5" t="inlineStr">
+      <c r="P134" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q127" s="5" t="inlineStr">
+      <c r="Q134" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R127" s="5" t="inlineStr">
+      <c r="R134" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S127" s="5" t="inlineStr">
+      <c r="S134" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T127" s="5" t="inlineStr">
+      <c r="T134" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U127" s="5" t="inlineStr">
+      <c r="U134" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V127" s="5" t="inlineStr">
+      <c r="V134" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W127" s="5" t="inlineStr">
+      <c r="W134" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X127" s="5" t="inlineStr">
+      <c r="X134" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y127" s="5" t="inlineStr">
+      <c r="Y134" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z127" s="5" t="inlineStr">
+      <c r="Z134" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA127" s="5" t="inlineStr">
+      <c r="AA134" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB127" s="5" t="inlineStr">
+      <c r="AB134" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC127" s="5" t="inlineStr">
+      <c r="AC134" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="9" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="E128" s="12" t="n">
+      <c r="E135" s="12" t="n">
         <v>-4352.488</v>
       </c>
-      <c r="I128" s="12" t="n">
+      <c r="I135" s="12" t="n">
         <v>392.964</v>
       </c>
-      <c r="M128" s="12" t="n">
+      <c r="M135" s="12" t="n">
         <v>278.404</v>
       </c>
-      <c r="O128" s="12" t="n">
+      <c r="O135" s="12" t="n">
         <v>5953.916</v>
       </c>
-      <c r="P128" s="12" t="n">
+      <c r="P135" s="12" t="n">
         <v>6062.304</v>
       </c>
-      <c r="Q128" s="12" t="n">
+      <c r="Q135" s="12" t="n">
         <v>3592.069</v>
       </c>
-      <c r="R128" s="12" t="n">
+      <c r="R135" s="12" t="n">
         <v>2558.671</v>
       </c>
-      <c r="S128" s="12" t="n">
+      <c r="S135" s="12" t="n">
         <v>1557.564</v>
       </c>
-      <c r="T128" s="12" t="n">
+      <c r="T135" s="12" t="n">
         <v>4015.007</v>
       </c>
-      <c r="U128" s="12" t="n">
+      <c r="U135" s="12" t="n">
         <v>213.933</v>
       </c>
-      <c r="V128" s="12" t="n">
+      <c r="V135" s="12" t="n">
         <v>-4352.488</v>
       </c>
-      <c r="W128" s="12" t="n">
+      <c r="W135" s="12" t="n">
         <v>392.964</v>
       </c>
-      <c r="X128" s="12" t="n">
+      <c r="X135" s="12" t="n">
         <v>278.404</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="E129" s="22" t="n">
-        <v>3110.34</v>
-      </c>
-      <c r="I129" s="22" t="n">
-        <v>1753.036</v>
-      </c>
-      <c r="M129" s="22" t="n">
-        <v>2337.543</v>
-      </c>
-      <c r="O129" s="22" t="n">
-        <v>2271.478</v>
-      </c>
-      <c r="P129" s="22" t="n">
-        <v>2979.519</v>
-      </c>
-      <c r="Q129" s="22" t="n">
-        <v>3414.358</v>
-      </c>
-      <c r="R129" s="22" t="n">
-        <v>3256.774</v>
-      </c>
-      <c r="S129" s="22" t="n">
-        <v>3291.338</v>
-      </c>
-      <c r="T129" s="22" t="n">
-        <v>3114.671</v>
-      </c>
-      <c r="U129" s="22" t="n">
-        <v>3307.537</v>
-      </c>
-      <c r="V129" s="22" t="n">
-        <v>3110.34</v>
-      </c>
-      <c r="W129" s="22" t="n">
-        <v>1753.036</v>
-      </c>
-      <c r="X129" s="22" t="n">
-        <v>2337.543</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="20" t="inlineStr">
-        <is>
-          <t>Depreciation And Amortization On Other Ope CF</t>
-        </is>
-      </c>
-      <c r="O130" s="22" t="n">
-        <v>76.664</v>
-      </c>
-      <c r="P130" s="22" t="n">
-        <v>73.551</v>
-      </c>
-      <c r="Q130" s="22" t="n">
-        <v>77.37</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="E131" s="22" t="n">
-        <v>3060.024</v>
-      </c>
-      <c r="I131" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" s="22" t="n">
-        <v>252.118</v>
-      </c>
-      <c r="O131" s="22" t="n">
-        <v>519.655</v>
-      </c>
-      <c r="P131" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" s="22" t="n">
-        <v>438.852</v>
-      </c>
-      <c r="R131" s="22" t="n">
-        <v>833.391</v>
-      </c>
-      <c r="S131" s="22" t="n">
-        <v>44.418</v>
-      </c>
-      <c r="T131" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U131" s="22" t="n">
-        <v>15.016</v>
-      </c>
-      <c r="V131" s="22" t="n">
-        <v>3060.024</v>
-      </c>
-      <c r="W131" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X131" s="22" t="n">
-        <v>252.118</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="20" t="inlineStr">
-        <is>
-          <t>영업권 상각</t>
-        </is>
-      </c>
-      <c r="E132" s="22" t="n">
-        <v>12.683</v>
-      </c>
-      <c r="I132" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" s="22" t="n">
-        <v>22.076</v>
-      </c>
-      <c r="P132" s="22" t="n">
-        <v>12.683</v>
-      </c>
-      <c r="Q132" s="22" t="n">
-        <v>12.683</v>
-      </c>
-      <c r="R132" s="22" t="n">
-        <v>12.683</v>
-      </c>
-      <c r="S132" s="22" t="n">
-        <v>12.683</v>
-      </c>
-      <c r="T132" s="22" t="n">
-        <v>12.683</v>
-      </c>
-      <c r="U132" s="22" t="n">
-        <v>12.683</v>
-      </c>
-      <c r="V132" s="22" t="n">
-        <v>12.683</v>
-      </c>
-      <c r="W132" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="20" t="inlineStr">
-        <is>
-          <t>고정자산 제각손실</t>
-        </is>
-      </c>
-      <c r="E133" s="22" t="n">
-        <v>36.954</v>
-      </c>
-      <c r="I133" s="22" t="n">
-        <v>41.741</v>
-      </c>
-      <c r="M133" s="22" t="n">
-        <v>160.352</v>
-      </c>
-      <c r="O133" s="22" t="n">
-        <v>12.993</v>
-      </c>
-      <c r="P133" s="22" t="n">
-        <v>104.433</v>
-      </c>
-      <c r="Q133" s="22" t="n">
-        <v>7.578</v>
-      </c>
-      <c r="R133" s="22" t="n">
-        <v>30.823</v>
-      </c>
-      <c r="S133" s="22" t="n">
-        <v>17.908</v>
-      </c>
-      <c r="T133" s="22" t="n">
-        <v>88.627</v>
-      </c>
-      <c r="U133" s="22" t="n">
-        <v>248.71</v>
-      </c>
-      <c r="V133" s="22" t="n">
-        <v>36.954</v>
-      </c>
-      <c r="W133" s="22" t="n">
-        <v>41.741</v>
-      </c>
-      <c r="X133" s="22" t="n">
-        <v>160.352</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="20" t="inlineStr">
-        <is>
-          <t>고정자산 매각손익</t>
-        </is>
-      </c>
-      <c r="E134" s="22" t="n">
-        <v>-50.4</v>
-      </c>
-      <c r="I134" s="22" t="n">
-        <v>-1.146</v>
-      </c>
-      <c r="M134" s="22" t="n">
-        <v>43.608</v>
-      </c>
-      <c r="O134" s="22" t="n">
-        <v>-0.022</v>
-      </c>
-      <c r="P134" s="22" t="n">
-        <v>-1.168</v>
-      </c>
-      <c r="Q134" s="22" t="n">
-        <v>-1.095</v>
-      </c>
-      <c r="R134" s="22" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="S134" s="22" t="n">
-        <v>-11.573</v>
-      </c>
-      <c r="T134" s="22" t="n">
-        <v>-11.239</v>
-      </c>
-      <c r="U134" s="22" t="n">
-        <v>-27.842</v>
-      </c>
-      <c r="V134" s="22" t="n">
-        <v>-50.4</v>
-      </c>
-      <c r="W134" s="22" t="n">
-        <v>-1.146</v>
-      </c>
-      <c r="X134" s="22" t="n">
-        <v>43.608</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="20" t="inlineStr">
-        <is>
-          <t>투자유가증권 매각손익</t>
-        </is>
-      </c>
-      <c r="E135" s="22" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="I135" s="22" t="n">
-        <v>-14.385</v>
-      </c>
-      <c r="M135" s="22" t="n">
-        <v>-6.52</v>
-      </c>
-      <c r="O135" s="22" t="n">
-        <v>-74.562</v>
-      </c>
-      <c r="P135" s="22" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="Q135" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" s="22" t="n">
-        <v>-4.031</v>
-      </c>
-      <c r="S135" s="22" t="n">
-        <v>-47.612</v>
-      </c>
-      <c r="T135" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" s="22" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="W135" s="22" t="n">
-        <v>-14.385</v>
-      </c>
-      <c r="X135" s="22" t="n">
-        <v>-6.52</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>부의 영업권 발생이익</t>
-        </is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="E136" s="22" t="n">
+        <v>3110.34</v>
+      </c>
+      <c r="I136" s="22" t="n">
+        <v>1753.036</v>
+      </c>
+      <c r="M136" s="22" t="n">
+        <v>2337.543</v>
       </c>
       <c r="O136" s="22" t="n">
-        <v>-324.506</v>
+        <v>2271.478</v>
       </c>
       <c r="P136" s="22" t="n">
-        <v>0</v>
+        <v>2979.519</v>
+      </c>
+      <c r="Q136" s="22" t="n">
+        <v>3414.358</v>
+      </c>
+      <c r="R136" s="22" t="n">
+        <v>3256.774</v>
+      </c>
+      <c r="S136" s="22" t="n">
+        <v>3291.338</v>
+      </c>
+      <c r="T136" s="22" t="n">
+        <v>3114.671</v>
+      </c>
+      <c r="U136" s="22" t="n">
+        <v>3307.537</v>
+      </c>
+      <c r="V136" s="22" t="n">
+        <v>3110.34</v>
+      </c>
+      <c r="W136" s="22" t="n">
+        <v>1753.036</v>
+      </c>
+      <c r="X136" s="22" t="n">
+        <v>2337.543</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손익</t>
-        </is>
-      </c>
-      <c r="I137" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" s="22" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="R137" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" s="22" t="n">
-        <v>3.784</v>
-      </c>
-      <c r="T137" s="22" t="n">
-        <v>3.089</v>
-      </c>
-      <c r="U137" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W137" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" s="22" t="n">
-        <v>0.357</v>
+          <t>Depreciation And Amortization On Other Ope CF</t>
+        </is>
+      </c>
+      <c r="O137" s="22" t="n">
+        <v>76.664</v>
+      </c>
+      <c r="P137" s="22" t="n">
+        <v>73.551</v>
+      </c>
+      <c r="Q137" s="22" t="n">
+        <v>77.37</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>대손충당금 증감</t>
-        </is>
+          <t>손상차손</t>
+        </is>
+      </c>
+      <c r="E138" s="22" t="n">
+        <v>3060.024</v>
+      </c>
+      <c r="I138" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="22" t="n">
+        <v>252.118</v>
       </c>
       <c r="O138" s="22" t="n">
-        <v>318.107</v>
+        <v>519.655</v>
       </c>
       <c r="P138" s="22" t="n">
-        <v>-304.145</v>
+        <v>0</v>
       </c>
       <c r="Q138" s="22" t="n">
-        <v>-3.235</v>
+        <v>438.852</v>
       </c>
       <c r="R138" s="22" t="n">
-        <v>-10.726</v>
+        <v>833.391</v>
       </c>
       <c r="S138" s="22" t="n">
+        <v>44.418</v>
+      </c>
+      <c r="T138" s="22" t="n">
         <v>0</v>
+      </c>
+      <c r="U138" s="22" t="n">
+        <v>15.016</v>
+      </c>
+      <c r="V138" s="22" t="n">
+        <v>3060.024</v>
+      </c>
+      <c r="W138" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" s="22" t="n">
+        <v>252.118</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>임원 퇴직위로 충당금 증감</t>
-        </is>
+          <t>영업권 상각</t>
+        </is>
+      </c>
+      <c r="E139" s="22" t="n">
+        <v>12.683</v>
+      </c>
+      <c r="I139" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="O139" s="22" t="n">
-        <v>-1464.986</v>
+        <v>22.076</v>
       </c>
       <c r="P139" s="22" t="n">
+        <v>12.683</v>
+      </c>
+      <c r="Q139" s="22" t="n">
+        <v>12.683</v>
+      </c>
+      <c r="R139" s="22" t="n">
+        <v>12.683</v>
+      </c>
+      <c r="S139" s="22" t="n">
+        <v>12.683</v>
+      </c>
+      <c r="T139" s="22" t="n">
+        <v>12.683</v>
+      </c>
+      <c r="U139" s="22" t="n">
+        <v>12.683</v>
+      </c>
+      <c r="V139" s="22" t="n">
+        <v>12.683</v>
+      </c>
+      <c r="W139" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>상여충당금 증감</t>
+          <t>고정자산 제각손실</t>
         </is>
       </c>
       <c r="E140" s="22" t="n">
-        <v>-31.935</v>
+        <v>36.954</v>
       </c>
       <c r="I140" s="22" t="n">
-        <v>-6.563</v>
+        <v>41.741</v>
       </c>
       <c r="M140" s="22" t="n">
-        <v>-1.626</v>
+        <v>160.352</v>
       </c>
       <c r="O140" s="22" t="n">
-        <v>30.476</v>
+        <v>12.993</v>
       </c>
       <c r="P140" s="22" t="n">
-        <v>50.734</v>
+        <v>104.433</v>
       </c>
       <c r="Q140" s="22" t="n">
-        <v>-42.092</v>
+        <v>7.578</v>
       </c>
       <c r="R140" s="22" t="n">
-        <v>-7.865</v>
+        <v>30.823</v>
       </c>
       <c r="S140" s="22" t="n">
-        <v>5.862</v>
+        <v>17.908</v>
       </c>
       <c r="T140" s="22" t="n">
-        <v>-66.899</v>
+        <v>88.627</v>
       </c>
       <c r="U140" s="22" t="n">
-        <v>-8.691000000000001</v>
+        <v>248.71</v>
       </c>
       <c r="V140" s="22" t="n">
-        <v>-31.935</v>
+        <v>36.954</v>
       </c>
       <c r="W140" s="22" t="n">
-        <v>-6.563</v>
+        <v>41.741</v>
       </c>
       <c r="X140" s="22" t="n">
-        <v>-1.626</v>
+        <v>160.352</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>퇴직급여자산 증감</t>
+          <t>고정자산 매각손익</t>
         </is>
       </c>
       <c r="E141" s="22" t="n">
-        <v>-108.037</v>
+        <v>-50.4</v>
       </c>
       <c r="I141" s="22" t="n">
-        <v>-266.223</v>
+        <v>-1.146</v>
       </c>
       <c r="M141" s="22" t="n">
-        <v>-240.551</v>
+        <v>43.608</v>
       </c>
       <c r="O141" s="22" t="n">
-        <v>82.68899999999999</v>
+        <v>-0.022</v>
       </c>
       <c r="P141" s="22" t="n">
-        <v>14.732</v>
+        <v>-1.168</v>
       </c>
       <c r="Q141" s="22" t="n">
-        <v>-23.509</v>
+        <v>-1.095</v>
       </c>
       <c r="R141" s="22" t="n">
-        <v>-36.254</v>
+        <v>0.345</v>
       </c>
       <c r="S141" s="22" t="n">
-        <v>-31.941</v>
+        <v>-11.573</v>
       </c>
       <c r="T141" s="22" t="n">
-        <v>-42.104</v>
+        <v>-11.239</v>
       </c>
       <c r="U141" s="22" t="n">
-        <v>-23.743</v>
+        <v>-27.842</v>
       </c>
       <c r="V141" s="22" t="n">
-        <v>-108.037</v>
+        <v>-50.4</v>
       </c>
       <c r="W141" s="22" t="n">
-        <v>-266.223</v>
+        <v>-1.146</v>
       </c>
       <c r="X141" s="22" t="n">
-        <v>-240.551</v>
+        <v>43.608</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>퇴직급여부채 증감</t>
+          <t>투자유가증권 매각손익</t>
         </is>
       </c>
       <c r="E142" s="22" t="n">
-        <v>30.314</v>
+        <v>-1.04</v>
       </c>
       <c r="I142" s="22" t="n">
-        <v>73.52</v>
+        <v>-14.385</v>
       </c>
       <c r="M142" s="22" t="n">
-        <v>85.94799999999999</v>
+        <v>-6.52</v>
       </c>
       <c r="O142" s="22" t="n">
-        <v>-36.642</v>
+        <v>-74.562</v>
       </c>
       <c r="P142" s="22" t="n">
-        <v>-2.929</v>
+        <v>-0.1</v>
       </c>
       <c r="Q142" s="22" t="n">
-        <v>-30.47</v>
+        <v>0</v>
       </c>
       <c r="R142" s="22" t="n">
-        <v>-35.782</v>
+        <v>-4.031</v>
       </c>
       <c r="S142" s="22" t="n">
-        <v>-46.175</v>
+        <v>-47.612</v>
       </c>
       <c r="T142" s="22" t="n">
-        <v>-61.702</v>
+        <v>0</v>
       </c>
       <c r="U142" s="22" t="n">
-        <v>-43.889</v>
+        <v>0</v>
       </c>
       <c r="V142" s="22" t="n">
-        <v>30.314</v>
+        <v>-1.04</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>73.52</v>
+        <v>-14.385</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>85.94799999999999</v>
+        <v>-6.52</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="E143" s="22" t="n">
-        <v>-58.59</v>
-      </c>
-      <c r="I143" s="22" t="n">
-        <v>-69.462</v>
-      </c>
-      <c r="M143" s="22" t="n">
-        <v>-110.475</v>
+          <t>부의 영업권 발생이익</t>
+        </is>
       </c>
       <c r="O143" s="22" t="n">
-        <v>-71.154</v>
+        <v>-324.506</v>
       </c>
       <c r="P143" s="22" t="n">
-        <v>-78.544</v>
-      </c>
-      <c r="Q143" s="22" t="n">
-        <v>-82.96299999999999</v>
-      </c>
-      <c r="R143" s="22" t="n">
-        <v>-61.658</v>
-      </c>
-      <c r="S143" s="22" t="n">
-        <v>-53.404</v>
-      </c>
-      <c r="T143" s="22" t="n">
-        <v>-73.843</v>
-      </c>
-      <c r="U143" s="22" t="n">
-        <v>-86.309</v>
-      </c>
-      <c r="V143" s="22" t="n">
-        <v>-58.59</v>
-      </c>
-      <c r="W143" s="22" t="n">
-        <v>-69.462</v>
-      </c>
-      <c r="X143" s="22" t="n">
-        <v>-110.475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="E144" s="22" t="n">
-        <v>3.949</v>
+          <t>투자유가증권 평가손익</t>
+        </is>
       </c>
       <c r="I144" s="22" t="n">
-        <v>6.638</v>
+        <v>0</v>
       </c>
       <c r="M144" s="22" t="n">
-        <v>78.48999999999999</v>
-      </c>
-      <c r="O144" s="22" t="n">
-        <v>13.215</v>
-      </c>
-      <c r="P144" s="22" t="n">
-        <v>11.697</v>
-      </c>
-      <c r="Q144" s="22" t="n">
-        <v>9.659000000000001</v>
+        <v>0.357</v>
       </c>
       <c r="R144" s="22" t="n">
-        <v>8.161</v>
+        <v>0</v>
       </c>
       <c r="S144" s="22" t="n">
-        <v>7.475</v>
+        <v>3.784</v>
       </c>
       <c r="T144" s="22" t="n">
-        <v>8.403</v>
+        <v>3.089</v>
       </c>
       <c r="U144" s="22" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="V144" s="22" t="n">
-        <v>3.949</v>
+        <v>0</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>6.638</v>
+        <v>0</v>
       </c>
       <c r="X144" s="22" t="n">
-        <v>78.48999999999999</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>외환차손익</t>
-        </is>
-      </c>
-      <c r="E145" s="22" t="n">
-        <v>-20.494</v>
-      </c>
-      <c r="I145" s="22" t="n">
-        <v>46.481</v>
-      </c>
-      <c r="M145" s="22" t="n">
-        <v>-44.939</v>
+          <t>대손충당금 증감</t>
+        </is>
       </c>
       <c r="O145" s="22" t="n">
-        <v>254.298</v>
+        <v>318.107</v>
       </c>
       <c r="P145" s="22" t="n">
-        <v>135.973</v>
+        <v>-304.145</v>
       </c>
       <c r="Q145" s="22" t="n">
-        <v>-31.495</v>
+        <v>-3.235</v>
       </c>
       <c r="R145" s="22" t="n">
-        <v>-37.186</v>
+        <v>-10.726</v>
       </c>
       <c r="S145" s="22" t="n">
-        <v>-18.785</v>
-      </c>
-      <c r="T145" s="22" t="n">
-        <v>-315.079</v>
-      </c>
-      <c r="U145" s="22" t="n">
-        <v>-128.483</v>
-      </c>
-      <c r="V145" s="22" t="n">
-        <v>-20.494</v>
-      </c>
-      <c r="W145" s="22" t="n">
-        <v>46.481</v>
-      </c>
-      <c r="X145" s="22" t="n">
-        <v>-44.939</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>지분법손익</t>
-        </is>
-      </c>
-      <c r="E146" s="22" t="n">
-        <v>9.981999999999999</v>
-      </c>
-      <c r="I146" s="22" t="n">
-        <v>-11.214</v>
-      </c>
-      <c r="M146" s="22" t="n">
-        <v>1.333</v>
+          <t>임원 퇴직위로 충당금 증감</t>
+        </is>
       </c>
       <c r="O146" s="22" t="n">
-        <v>-91.256</v>
+        <v>-1464.986</v>
       </c>
       <c r="P146" s="22" t="n">
-        <v>-36.858</v>
-      </c>
-      <c r="Q146" s="22" t="n">
-        <v>-72.747</v>
-      </c>
-      <c r="R146" s="22" t="n">
-        <v>-43.175</v>
-      </c>
-      <c r="S146" s="22" t="n">
-        <v>-58.919</v>
-      </c>
-      <c r="T146" s="22" t="n">
-        <v>-12.817</v>
-      </c>
-      <c r="U146" s="22" t="n">
-        <v>3.602</v>
-      </c>
-      <c r="V146" s="22" t="n">
-        <v>9.981999999999999</v>
-      </c>
-      <c r="W146" s="22" t="n">
-        <v>-11.214</v>
-      </c>
-      <c r="X146" s="22" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>보험해약 손익</t>
-        </is>
+          <t>상여충당금 증감</t>
+        </is>
+      </c>
+      <c r="E147" s="22" t="n">
+        <v>-31.935</v>
+      </c>
+      <c r="I147" s="22" t="n">
+        <v>-6.563</v>
+      </c>
+      <c r="M147" s="22" t="n">
+        <v>-1.626</v>
       </c>
       <c r="O147" s="22" t="n">
-        <v>54.514</v>
+        <v>30.476</v>
       </c>
       <c r="P147" s="22" t="n">
-        <v>0</v>
+        <v>50.734</v>
+      </c>
+      <c r="Q147" s="22" t="n">
+        <v>-42.092</v>
+      </c>
+      <c r="R147" s="22" t="n">
+        <v>-7.865</v>
+      </c>
+      <c r="S147" s="22" t="n">
+        <v>5.862</v>
+      </c>
+      <c r="T147" s="22" t="n">
+        <v>-66.899</v>
+      </c>
+      <c r="U147" s="22" t="n">
+        <v>-8.691000000000001</v>
+      </c>
+      <c r="V147" s="22" t="n">
+        <v>-31.935</v>
+      </c>
+      <c r="W147" s="22" t="n">
+        <v>-6.563</v>
+      </c>
+      <c r="X147" s="22" t="n">
+        <v>-1.626</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>임대료 수익</t>
+          <t>퇴직급여자산 증감</t>
         </is>
       </c>
       <c r="E148" s="22" t="n">
-        <v>-31.397</v>
+        <v>-108.037</v>
       </c>
       <c r="I148" s="22" t="n">
-        <v>-30.821</v>
+        <v>-266.223</v>
       </c>
       <c r="M148" s="22" t="n">
-        <v>-37.486</v>
+        <v>-240.551</v>
+      </c>
+      <c r="O148" s="22" t="n">
+        <v>82.68899999999999</v>
+      </c>
+      <c r="P148" s="22" t="n">
+        <v>14.732</v>
+      </c>
+      <c r="Q148" s="22" t="n">
+        <v>-23.509</v>
+      </c>
+      <c r="R148" s="22" t="n">
+        <v>-36.254</v>
+      </c>
+      <c r="S148" s="22" t="n">
+        <v>-31.941</v>
       </c>
       <c r="T148" s="22" t="n">
-        <v>-34.468</v>
+        <v>-42.104</v>
       </c>
       <c r="U148" s="22" t="n">
-        <v>-33.014</v>
+        <v>-23.743</v>
       </c>
       <c r="V148" s="22" t="n">
-        <v>-31.397</v>
+        <v>-108.037</v>
       </c>
       <c r="W148" s="22" t="n">
-        <v>-30.821</v>
+        <v>-266.223</v>
       </c>
       <c r="X148" s="22" t="n">
-        <v>-37.486</v>
+        <v>-240.551</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
+          <t>퇴직급여부채 증감</t>
         </is>
       </c>
       <c r="E149" s="22" t="n">
-        <v>-29.896</v>
+        <v>30.314</v>
       </c>
       <c r="I149" s="22" t="n">
-        <v>0</v>
+        <v>73.52</v>
+      </c>
+      <c r="M149" s="22" t="n">
+        <v>85.94799999999999</v>
+      </c>
+      <c r="O149" s="22" t="n">
+        <v>-36.642</v>
+      </c>
+      <c r="P149" s="22" t="n">
+        <v>-2.929</v>
+      </c>
+      <c r="Q149" s="22" t="n">
+        <v>-30.47</v>
+      </c>
+      <c r="R149" s="22" t="n">
+        <v>-35.782</v>
+      </c>
+      <c r="S149" s="22" t="n">
+        <v>-46.175</v>
+      </c>
+      <c r="T149" s="22" t="n">
+        <v>-61.702</v>
       </c>
       <c r="U149" s="22" t="n">
-        <v>-13.997</v>
+        <v>-43.889</v>
       </c>
       <c r="V149" s="22" t="n">
-        <v>-29.896</v>
+        <v>30.314</v>
       </c>
       <c r="W149" s="22" t="n">
-        <v>0</v>
+        <v>73.52</v>
+      </c>
+      <c r="X149" s="22" t="n">
+        <v>85.94799999999999</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>환경대책비</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="E150" s="22" t="n">
-        <v>19.59</v>
+        <v>-58.59</v>
       </c>
       <c r="I150" s="22" t="n">
-        <v>0</v>
+        <v>-69.462</v>
+      </c>
+      <c r="M150" s="22" t="n">
+        <v>-110.475</v>
+      </c>
+      <c r="O150" s="22" t="n">
+        <v>-71.154</v>
+      </c>
+      <c r="P150" s="22" t="n">
+        <v>-78.544</v>
+      </c>
+      <c r="Q150" s="22" t="n">
+        <v>-82.96299999999999</v>
+      </c>
+      <c r="R150" s="22" t="n">
+        <v>-61.658</v>
+      </c>
+      <c r="S150" s="22" t="n">
+        <v>-53.404</v>
       </c>
       <c r="T150" s="22" t="n">
-        <v>0</v>
+        <v>-73.843</v>
       </c>
       <c r="U150" s="22" t="n">
-        <v>51.467</v>
+        <v>-86.309</v>
       </c>
       <c r="V150" s="22" t="n">
-        <v>19.59</v>
+        <v>-58.59</v>
       </c>
       <c r="W150" s="22" t="n">
-        <v>0</v>
+        <v>-69.462</v>
+      </c>
+      <c r="X150" s="22" t="n">
+        <v>-110.475</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="E151" s="22" t="n">
-        <v>156.948</v>
+        <v>3.949</v>
       </c>
       <c r="I151" s="22" t="n">
-        <v>-715.559</v>
+        <v>6.638</v>
       </c>
       <c r="M151" s="22" t="n">
-        <v>-1181.954</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="O151" s="22" t="n">
-        <v>-2006.493</v>
+        <v>13.215</v>
       </c>
       <c r="P151" s="22" t="n">
-        <v>-258.276</v>
+        <v>11.697</v>
       </c>
       <c r="Q151" s="22" t="n">
-        <v>2415.924</v>
+        <v>9.659000000000001</v>
       </c>
       <c r="R151" s="22" t="n">
-        <v>-2000.63</v>
+        <v>8.161</v>
       </c>
       <c r="S151" s="22" t="n">
-        <v>-163.083</v>
+        <v>7.475</v>
       </c>
       <c r="T151" s="22" t="n">
-        <v>-594.546</v>
+        <v>8.403</v>
       </c>
       <c r="U151" s="22" t="n">
-        <v>3298.575</v>
+        <v>4.73</v>
       </c>
       <c r="V151" s="22" t="n">
-        <v>156.948</v>
+        <v>3.949</v>
       </c>
       <c r="W151" s="22" t="n">
-        <v>-715.559</v>
+        <v>6.638</v>
       </c>
       <c r="X151" s="22" t="n">
-        <v>-1181.954</v>
+        <v>78.48999999999999</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
+          <t>외환차손익</t>
         </is>
       </c>
       <c r="E152" s="22" t="n">
-        <v>505.175</v>
+        <v>-20.494</v>
       </c>
       <c r="I152" s="22" t="n">
-        <v>-36.296</v>
+        <v>46.481</v>
       </c>
       <c r="M152" s="22" t="n">
-        <v>-2003.698</v>
+        <v>-44.939</v>
       </c>
       <c r="O152" s="22" t="n">
-        <v>-28.494</v>
+        <v>254.298</v>
       </c>
       <c r="P152" s="22" t="n">
-        <v>-127.78</v>
+        <v>135.973</v>
       </c>
       <c r="Q152" s="22" t="n">
-        <v>-29.554</v>
+        <v>-31.495</v>
       </c>
       <c r="R152" s="22" t="n">
-        <v>-253.274</v>
+        <v>-37.186</v>
       </c>
       <c r="S152" s="22" t="n">
-        <v>-98.157</v>
+        <v>-18.785</v>
       </c>
       <c r="T152" s="22" t="n">
-        <v>-627.686</v>
+        <v>-315.079</v>
       </c>
       <c r="U152" s="22" t="n">
-        <v>-435.652</v>
+        <v>-128.483</v>
       </c>
       <c r="V152" s="22" t="n">
-        <v>505.175</v>
+        <v>-20.494</v>
       </c>
       <c r="W152" s="22" t="n">
-        <v>-36.296</v>
+        <v>46.481</v>
       </c>
       <c r="X152" s="22" t="n">
-        <v>-2003.698</v>
+        <v>-44.939</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>기타 자산 증감</t>
-        </is>
+          <t>지분법손익</t>
+        </is>
+      </c>
+      <c r="E153" s="22" t="n">
+        <v>9.981999999999999</v>
+      </c>
+      <c r="I153" s="22" t="n">
+        <v>-11.214</v>
+      </c>
+      <c r="M153" s="22" t="n">
+        <v>1.333</v>
       </c>
       <c r="O153" s="22" t="n">
-        <v>40.026</v>
+        <v>-91.256</v>
       </c>
       <c r="P153" s="22" t="n">
-        <v>-175.845</v>
+        <v>-36.858</v>
+      </c>
+      <c r="Q153" s="22" t="n">
+        <v>-72.747</v>
+      </c>
+      <c r="R153" s="22" t="n">
+        <v>-43.175</v>
+      </c>
+      <c r="S153" s="22" t="n">
+        <v>-58.919</v>
+      </c>
+      <c r="T153" s="22" t="n">
+        <v>-12.817</v>
+      </c>
+      <c r="U153" s="22" t="n">
+        <v>3.602</v>
+      </c>
+      <c r="V153" s="22" t="n">
+        <v>9.981999999999999</v>
+      </c>
+      <c r="W153" s="22" t="n">
+        <v>-11.214</v>
+      </c>
+      <c r="X153" s="22" t="n">
+        <v>1.333</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
-        </is>
-      </c>
-      <c r="E154" s="22" t="n">
-        <v>153.896</v>
-      </c>
-      <c r="I154" s="22" t="n">
-        <v>91.58499999999999</v>
-      </c>
-      <c r="M154" s="22" t="n">
-        <v>-516.329</v>
+          <t>보험해약 손익</t>
+        </is>
       </c>
       <c r="O154" s="22" t="n">
-        <v>890.438</v>
+        <v>54.514</v>
       </c>
       <c r="P154" s="22" t="n">
-        <v>414.826</v>
-      </c>
-      <c r="Q154" s="22" t="n">
-        <v>-566.152</v>
-      </c>
-      <c r="R154" s="22" t="n">
-        <v>-270.572</v>
-      </c>
-      <c r="S154" s="22" t="n">
-        <v>373.481</v>
-      </c>
-      <c r="T154" s="22" t="n">
-        <v>-360.433</v>
-      </c>
-      <c r="U154" s="22" t="n">
-        <v>-1493.565</v>
-      </c>
-      <c r="V154" s="22" t="n">
-        <v>153.896</v>
-      </c>
-      <c r="W154" s="22" t="n">
-        <v>91.58499999999999</v>
-      </c>
-      <c r="X154" s="22" t="n">
-        <v>-516.329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>기타 부채 증감</t>
-        </is>
-      </c>
-      <c r="O155" s="22" t="n">
-        <v>594.42</v>
-      </c>
-      <c r="P155" s="22" t="n">
-        <v>464.081</v>
+          <t>임대료 수익</t>
+        </is>
+      </c>
+      <c r="E155" s="22" t="n">
+        <v>-31.397</v>
+      </c>
+      <c r="I155" s="22" t="n">
+        <v>-30.821</v>
+      </c>
+      <c r="M155" s="22" t="n">
+        <v>-37.486</v>
+      </c>
+      <c r="T155" s="22" t="n">
+        <v>-34.468</v>
+      </c>
+      <c r="U155" s="22" t="n">
+        <v>-33.014</v>
+      </c>
+      <c r="V155" s="22" t="n">
+        <v>-31.397</v>
+      </c>
+      <c r="W155" s="22" t="n">
+        <v>-30.821</v>
+      </c>
+      <c r="X155" s="22" t="n">
+        <v>-37.486</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="E156" s="22" t="n">
-        <v>-223.059</v>
+        <v>-29.896</v>
       </c>
       <c r="I156" s="22" t="n">
-        <v>116.731</v>
-      </c>
-      <c r="M156" s="22" t="n">
-        <v>1790.335</v>
-      </c>
-      <c r="P156" s="22" t="n">
-        <v>288.135</v>
-      </c>
-      <c r="Q156" s="22" t="n">
-        <v>71.078</v>
-      </c>
-      <c r="R156" s="22" t="n">
-        <v>749.4880000000001</v>
-      </c>
-      <c r="S156" s="22" t="n">
-        <v>515.992</v>
-      </c>
-      <c r="T156" s="22" t="n">
-        <v>-922.999</v>
+        <v>0</v>
       </c>
       <c r="U156" s="22" t="n">
-        <v>-95.895</v>
+        <v>-13.997</v>
       </c>
       <c r="V156" s="22" t="n">
-        <v>-223.059</v>
+        <v>-29.896</v>
       </c>
       <c r="W156" s="22" t="n">
-        <v>116.731</v>
-      </c>
-      <c r="X156" s="22" t="n">
-        <v>1790.335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>환경대책비</t>
         </is>
       </c>
       <c r="E157" s="22" t="n">
-        <v>2192.519</v>
+        <v>19.59</v>
       </c>
       <c r="I157" s="22" t="n">
-        <v>1371.027</v>
-      </c>
-      <c r="M157" s="22" t="n">
-        <v>884.91</v>
-      </c>
-      <c r="O157" s="22" t="n">
-        <v>7036.85</v>
-      </c>
-      <c r="P157" s="22" t="n">
-        <v>9338.887000000001</v>
-      </c>
-      <c r="Q157" s="22" t="n">
-        <v>9078.888000000001</v>
-      </c>
-      <c r="R157" s="22" t="n">
-        <v>4689.182</v>
-      </c>
-      <c r="S157" s="22" t="n">
-        <v>5300.856</v>
+        <v>0</v>
       </c>
       <c r="T157" s="22" t="n">
-        <v>4118.661</v>
+        <v>0</v>
       </c>
       <c r="U157" s="22" t="n">
-        <v>4765.172</v>
+        <v>51.467</v>
       </c>
       <c r="V157" s="22" t="n">
-        <v>2192.519</v>
+        <v>19.59</v>
       </c>
       <c r="W157" s="22" t="n">
-        <v>1371.027</v>
-      </c>
-      <c r="X157" s="22" t="n">
-        <v>884.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="E158" s="22" t="n">
-        <v>63.392</v>
+        <v>156.948</v>
       </c>
       <c r="I158" s="22" t="n">
-        <v>71.878</v>
+        <v>-715.559</v>
       </c>
       <c r="M158" s="22" t="n">
-        <v>115.103</v>
+        <v>-1181.954</v>
       </c>
       <c r="O158" s="22" t="n">
-        <v>123.692</v>
+        <v>-2006.493</v>
       </c>
       <c r="P158" s="22" t="n">
-        <v>104.733</v>
+        <v>-258.276</v>
       </c>
       <c r="Q158" s="22" t="n">
-        <v>100.062</v>
+        <v>2415.924</v>
       </c>
       <c r="R158" s="22" t="n">
-        <v>84.369</v>
+        <v>-2000.63</v>
       </c>
       <c r="S158" s="22" t="n">
-        <v>70.36</v>
+        <v>-163.083</v>
       </c>
       <c r="T158" s="22" t="n">
-        <v>91.18300000000001</v>
+        <v>-594.546</v>
       </c>
       <c r="U158" s="22" t="n">
-        <v>92.428</v>
+        <v>3298.575</v>
       </c>
       <c r="V158" s="22" t="n">
-        <v>63.392</v>
+        <v>156.948</v>
       </c>
       <c r="W158" s="22" t="n">
-        <v>71.878</v>
+        <v>-715.559</v>
       </c>
       <c r="X158" s="22" t="n">
-        <v>115.103</v>
+        <v>-1181.954</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>재고자산 증감</t>
         </is>
       </c>
       <c r="E159" s="22" t="n">
-        <v>-3.997</v>
+        <v>505.175</v>
       </c>
       <c r="I159" s="22" t="n">
-        <v>-6.857</v>
+        <v>-36.296</v>
       </c>
       <c r="M159" s="22" t="n">
-        <v>-78.505</v>
+        <v>-2003.698</v>
       </c>
       <c r="O159" s="22" t="n">
-        <v>-12.544</v>
+        <v>-28.494</v>
       </c>
       <c r="P159" s="22" t="n">
-        <v>-11.232</v>
+        <v>-127.78</v>
       </c>
       <c r="Q159" s="22" t="n">
-        <v>-9.598000000000001</v>
+        <v>-29.554</v>
       </c>
       <c r="R159" s="22" t="n">
-        <v>-7.706</v>
+        <v>-253.274</v>
       </c>
       <c r="S159" s="22" t="n">
-        <v>-7.943</v>
+        <v>-98.157</v>
       </c>
       <c r="T159" s="22" t="n">
-        <v>-7.797</v>
+        <v>-627.686</v>
       </c>
       <c r="U159" s="22" t="n">
-        <v>-5.179</v>
+        <v>-435.652</v>
       </c>
       <c r="V159" s="22" t="n">
-        <v>-3.997</v>
+        <v>505.175</v>
       </c>
       <c r="W159" s="22" t="n">
-        <v>-6.857</v>
+        <v>-36.296</v>
       </c>
       <c r="X159" s="22" t="n">
-        <v>-78.505</v>
+        <v>-2003.698</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Rent Income Ope CF</t>
-        </is>
-      </c>
-      <c r="E160" s="22" t="n">
-        <v>31.397</v>
-      </c>
-      <c r="I160" s="22" t="n">
-        <v>30.203</v>
-      </c>
-      <c r="M160" s="22" t="n">
-        <v>37.519</v>
-      </c>
-      <c r="T160" s="22" t="n">
-        <v>34.468</v>
-      </c>
-      <c r="U160" s="22" t="n">
-        <v>32.69</v>
-      </c>
-      <c r="V160" s="22" t="n">
-        <v>31.397</v>
-      </c>
-      <c r="W160" s="22" t="n">
-        <v>30.203</v>
-      </c>
-      <c r="X160" s="22" t="n">
-        <v>37.519</v>
+          <t>기타 자산 증감</t>
+        </is>
+      </c>
+      <c r="O160" s="22" t="n">
+        <v>40.026</v>
+      </c>
+      <c r="P160" s="22" t="n">
+        <v>-175.845</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>보조금 수취</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="E161" s="22" t="n">
-        <v>29.896</v>
+        <v>153.896</v>
       </c>
       <c r="I161" s="22" t="n">
-        <v>0</v>
+        <v>91.58499999999999</v>
+      </c>
+      <c r="M161" s="22" t="n">
+        <v>-516.329</v>
+      </c>
+      <c r="O161" s="22" t="n">
+        <v>890.438</v>
+      </c>
+      <c r="P161" s="22" t="n">
+        <v>414.826</v>
+      </c>
+      <c r="Q161" s="22" t="n">
+        <v>-566.152</v>
+      </c>
+      <c r="R161" s="22" t="n">
+        <v>-270.572</v>
+      </c>
+      <c r="S161" s="22" t="n">
+        <v>373.481</v>
       </c>
       <c r="T161" s="22" t="n">
-        <v>0</v>
+        <v>-360.433</v>
       </c>
       <c r="U161" s="22" t="n">
-        <v>365.301</v>
+        <v>-1493.565</v>
       </c>
       <c r="V161" s="22" t="n">
-        <v>29.896</v>
+        <v>153.896</v>
       </c>
       <c r="W161" s="22" t="n">
-        <v>0</v>
+        <v>91.58499999999999</v>
+      </c>
+      <c r="X161" s="22" t="n">
+        <v>-516.329</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="20" t="inlineStr">
         <is>
-          <t>Environmental Expenses Paid Ope CF</t>
-        </is>
-      </c>
-      <c r="E162" s="22" t="n">
-        <v>-75.64</v>
-      </c>
-      <c r="I162" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T162" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U162" s="22" t="n">
-        <v>-33.987</v>
-      </c>
-      <c r="V162" s="22" t="n">
-        <v>-75.64</v>
-      </c>
-      <c r="W162" s="22" t="n">
-        <v>0</v>
+          <t>기타 부채 증감</t>
+        </is>
+      </c>
+      <c r="O162" s="22" t="n">
+        <v>594.42</v>
+      </c>
+      <c r="P162" s="22" t="n">
+        <v>464.081</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부·환급</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E163" s="22" t="n">
-        <v>467.596</v>
-      </c>
-      <c r="O163" s="22" t="n">
-        <v>-1289.413</v>
+        <v>-223.059</v>
+      </c>
+      <c r="I163" s="22" t="n">
+        <v>116.731</v>
+      </c>
+      <c r="M163" s="22" t="n">
+        <v>1790.335</v>
       </c>
       <c r="P163" s="22" t="n">
-        <v>-1264.487</v>
+        <v>288.135</v>
       </c>
       <c r="Q163" s="22" t="n">
-        <v>-1688.401</v>
+        <v>71.078</v>
       </c>
       <c r="R163" s="22" t="n">
-        <v>-1284.77</v>
+        <v>749.4880000000001</v>
       </c>
       <c r="S163" s="22" t="n">
-        <v>-787.572</v>
+        <v>515.992</v>
       </c>
       <c r="T163" s="22" t="n">
-        <v>-205.397</v>
+        <v>-922.999</v>
       </c>
       <c r="U163" s="22" t="n">
-        <v>-1628.164</v>
+        <v>-95.895</v>
       </c>
       <c r="V163" s="22" t="n">
-        <v>467.596</v>
+        <v>-223.059</v>
+      </c>
+      <c r="W163" s="22" t="n">
+        <v>116.731</v>
+      </c>
+      <c r="X163" s="22" t="n">
+        <v>1790.335</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20" t="inlineStr">
         <is>
-          <t>Payments For Directors Retirement Benefits Ope CF</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="E164" s="22" t="n">
-        <v>0</v>
+        <v>2192.519</v>
       </c>
       <c r="I164" s="22" t="n">
-        <v>-15.624</v>
+        <v>1371.027</v>
       </c>
       <c r="M164" s="22" t="n">
-        <v>0</v>
+        <v>884.91</v>
+      </c>
+      <c r="O164" s="22" t="n">
+        <v>7036.85</v>
+      </c>
+      <c r="P164" s="22" t="n">
+        <v>9338.887000000001</v>
+      </c>
+      <c r="Q164" s="22" t="n">
+        <v>9078.888000000001</v>
+      </c>
+      <c r="R164" s="22" t="n">
+        <v>4689.182</v>
+      </c>
+      <c r="S164" s="22" t="n">
+        <v>5300.856</v>
+      </c>
+      <c r="T164" s="22" t="n">
+        <v>4118.661</v>
+      </c>
+      <c r="U164" s="22" t="n">
+        <v>4765.172</v>
       </c>
       <c r="V164" s="22" t="n">
-        <v>0</v>
+        <v>2192.519</v>
       </c>
       <c r="W164" s="22" t="n">
-        <v>-15.624</v>
+        <v>1371.027</v>
       </c>
       <c r="X164" s="22" t="n">
-        <v>0</v>
+        <v>884.91</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>이자·배당금 수취</t>
         </is>
       </c>
       <c r="E165" s="22" t="n">
-        <v>-27.369</v>
+        <v>63.392</v>
       </c>
       <c r="I165" s="22" t="n">
-        <v>-17.612</v>
+        <v>71.878</v>
       </c>
       <c r="M165" s="22" t="n">
-        <v>-92.08199999999999</v>
+        <v>115.103</v>
+      </c>
+      <c r="O165" s="22" t="n">
+        <v>123.692</v>
+      </c>
+      <c r="P165" s="22" t="n">
+        <v>104.733</v>
+      </c>
+      <c r="Q165" s="22" t="n">
+        <v>100.062</v>
+      </c>
+      <c r="R165" s="22" t="n">
+        <v>84.369</v>
+      </c>
+      <c r="S165" s="22" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="T165" s="22" t="n">
+        <v>91.18300000000001</v>
+      </c>
+      <c r="U165" s="22" t="n">
+        <v>92.428</v>
       </c>
       <c r="V165" s="22" t="n">
-        <v>-27.369</v>
+        <v>63.392</v>
       </c>
       <c r="W165" s="22" t="n">
-        <v>-17.612</v>
+        <v>71.878</v>
       </c>
       <c r="X165" s="22" t="n">
-        <v>-92.08199999999999</v>
+        <v>115.103</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="20" t="inlineStr">
         <is>
-          <t>법인세 환급</t>
+          <t>이자 지급</t>
         </is>
       </c>
       <c r="E166" s="22" t="n">
-        <v>494.965</v>
+        <v>-3.997</v>
       </c>
       <c r="I166" s="22" t="n">
-        <v>17.56</v>
+        <v>-6.857</v>
       </c>
       <c r="M166" s="22" t="n">
-        <v>11.957</v>
+        <v>-78.505</v>
+      </c>
+      <c r="O166" s="22" t="n">
+        <v>-12.544</v>
+      </c>
+      <c r="P166" s="22" t="n">
+        <v>-11.232</v>
+      </c>
+      <c r="Q166" s="22" t="n">
+        <v>-9.598000000000001</v>
+      </c>
+      <c r="R166" s="22" t="n">
+        <v>-7.706</v>
+      </c>
+      <c r="S166" s="22" t="n">
+        <v>-7.943</v>
+      </c>
+      <c r="T166" s="22" t="n">
+        <v>-7.797</v>
+      </c>
+      <c r="U166" s="22" t="n">
+        <v>-5.179</v>
       </c>
       <c r="V166" s="22" t="n">
-        <v>494.965</v>
+        <v>-3.997</v>
       </c>
       <c r="W166" s="22" t="n">
-        <v>17.56</v>
+        <v>-6.857</v>
       </c>
       <c r="X166" s="22" t="n">
-        <v>11.957</v>
+        <v>-78.505</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E167" s="12" t="n">
-        <v>2705.164</v>
-      </c>
-      <c r="I167" s="12" t="n">
-        <v>1450.576</v>
-      </c>
-      <c r="M167" s="12" t="n">
-        <v>878.904</v>
-      </c>
-      <c r="O167" s="12" t="n">
-        <v>5858.584</v>
-      </c>
-      <c r="P167" s="12" t="n">
-        <v>8167.901</v>
-      </c>
-      <c r="Q167" s="12" t="n">
-        <v>7480.95</v>
-      </c>
-      <c r="R167" s="12" t="n">
-        <v>3481.075</v>
-      </c>
-      <c r="S167" s="12" t="n">
-        <v>4575.701</v>
-      </c>
-      <c r="T167" s="12" t="n">
-        <v>4031.117</v>
-      </c>
-      <c r="U167" s="12" t="n">
-        <v>3588.261</v>
-      </c>
-      <c r="V167" s="12" t="n">
-        <v>2705.164</v>
-      </c>
-      <c r="W167" s="12" t="n">
-        <v>1450.576</v>
-      </c>
-      <c r="X167" s="12" t="n">
-        <v>878.904</v>
+      <c r="A167" s="20" t="inlineStr">
+        <is>
+          <t>Proceeds From Rent Income Ope CF</t>
+        </is>
+      </c>
+      <c r="E167" s="22" t="n">
+        <v>31.397</v>
+      </c>
+      <c r="I167" s="22" t="n">
+        <v>30.203</v>
+      </c>
+      <c r="M167" s="22" t="n">
+        <v>37.519</v>
+      </c>
+      <c r="T167" s="22" t="n">
+        <v>34.468</v>
+      </c>
+      <c r="U167" s="22" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="V167" s="22" t="n">
+        <v>31.397</v>
+      </c>
+      <c r="W167" s="22" t="n">
+        <v>30.203</v>
+      </c>
+      <c r="X167" s="22" t="n">
+        <v>37.519</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="20" t="inlineStr">
         <is>
-          <t>정기예금 예입</t>
+          <t>보조금 수취</t>
         </is>
       </c>
       <c r="E168" s="22" t="n">
+        <v>29.896</v>
+      </c>
+      <c r="I168" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I168" s="22" t="n">
-        <v>-4000</v>
-      </c>
-      <c r="M168" s="22" t="n">
+      <c r="T168" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O168" s="22" t="n">
-        <v>-1128.7</v>
-      </c>
-      <c r="P168" s="22" t="n">
-        <v>0</v>
+      <c r="U168" s="22" t="n">
+        <v>365.301</v>
       </c>
       <c r="V168" s="22" t="n">
-        <v>0</v>
+        <v>29.896</v>
       </c>
       <c r="W168" s="22" t="n">
-        <v>-4000</v>
-      </c>
-      <c r="X168" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="20" t="inlineStr">
         <is>
-          <t>정기예금 인출</t>
-        </is>
+          <t>Environmental Expenses Paid Ope CF</t>
+        </is>
+      </c>
+      <c r="E169" s="22" t="n">
+        <v>-75.64</v>
       </c>
       <c r="I169" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M169" s="22" t="n">
-        <v>4000</v>
-      </c>
-      <c r="P169" s="22" t="n">
+      <c r="T169" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" s="22" t="n">
-        <v>1128.7</v>
-      </c>
-      <c r="R169" s="22" t="n">
-        <v>0</v>
+      <c r="U169" s="22" t="n">
+        <v>-33.987</v>
+      </c>
+      <c r="V169" s="22" t="n">
+        <v>-75.64</v>
       </c>
       <c r="W169" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="X169" s="22" t="n">
-        <v>4000</v>
-      </c>
     </row>
     <row r="170">
       <c r="A170" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>법인세 납부·환급</t>
         </is>
       </c>
       <c r="E170" s="22" t="n">
-        <v>-2943.406</v>
-      </c>
-      <c r="I170" s="22" t="n">
-        <v>-3851.746</v>
-      </c>
-      <c r="M170" s="22" t="n">
-        <v>-11359.851</v>
+        <v>467.596</v>
       </c>
       <c r="O170" s="22" t="n">
-        <v>-2747.07</v>
+        <v>-1289.413</v>
       </c>
       <c r="P170" s="22" t="n">
-        <v>-4744.546</v>
+        <v>-1264.487</v>
       </c>
       <c r="Q170" s="22" t="n">
-        <v>-4037.514</v>
+        <v>-1688.401</v>
       </c>
       <c r="R170" s="22" t="n">
-        <v>-3929.121</v>
+        <v>-1284.77</v>
       </c>
       <c r="S170" s="22" t="n">
-        <v>-2488.374</v>
+        <v>-787.572</v>
       </c>
       <c r="T170" s="22" t="n">
-        <v>-2678.123</v>
+        <v>-205.397</v>
       </c>
       <c r="U170" s="22" t="n">
-        <v>-3725.477</v>
+        <v>-1628.164</v>
       </c>
       <c r="V170" s="22" t="n">
-        <v>-2943.406</v>
-      </c>
-      <c r="W170" s="22" t="n">
-        <v>-3851.746</v>
-      </c>
-      <c r="X170" s="22" t="n">
-        <v>-11359.851</v>
+        <v>467.596</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="20" t="inlineStr">
         <is>
-          <t>유형자산 제각 지출</t>
+          <t>Payments For Directors Retirement Benefits Ope CF</t>
         </is>
       </c>
       <c r="E171" s="22" t="n">
-        <v>-137.999</v>
+        <v>0</v>
       </c>
       <c r="I171" s="22" t="n">
-        <v>-33.658</v>
+        <v>-15.624</v>
       </c>
       <c r="M171" s="22" t="n">
-        <v>-135.607</v>
-      </c>
-      <c r="O171" s="22" t="n">
-        <v>-1.616</v>
-      </c>
-      <c r="P171" s="22" t="n">
-        <v>-3.558</v>
-      </c>
-      <c r="Q171" s="22" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="R171" s="22" t="n">
-        <v>-8.971</v>
-      </c>
-      <c r="S171" s="22" t="n">
-        <v>-5.159</v>
-      </c>
-      <c r="T171" s="22" t="n">
-        <v>-14.4</v>
-      </c>
-      <c r="U171" s="22" t="n">
-        <v>-47.657</v>
+        <v>0</v>
       </c>
       <c r="V171" s="22" t="n">
-        <v>-137.999</v>
+        <v>0</v>
       </c>
       <c r="W171" s="22" t="n">
-        <v>-33.658</v>
+        <v>-15.624</v>
       </c>
       <c r="X171" s="22" t="n">
-        <v>-135.607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
+          <t>법인세 납부</t>
         </is>
       </c>
       <c r="E172" s="22" t="n">
-        <v>167.063</v>
+        <v>-27.369</v>
       </c>
       <c r="I172" s="22" t="n">
-        <v>2.381</v>
+        <v>-17.612</v>
       </c>
       <c r="M172" s="22" t="n">
-        <v>3.443</v>
-      </c>
-      <c r="O172" s="22" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="P172" s="22" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="Q172" s="22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="R172" s="22" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="S172" s="22" t="n">
-        <v>12.529</v>
-      </c>
-      <c r="T172" s="22" t="n">
-        <v>14.148</v>
-      </c>
-      <c r="U172" s="22" t="n">
-        <v>28.618</v>
+        <v>-92.08199999999999</v>
       </c>
       <c r="V172" s="22" t="n">
-        <v>167.063</v>
+        <v>-27.369</v>
       </c>
       <c r="W172" s="22" t="n">
-        <v>2.381</v>
+        <v>-17.612</v>
       </c>
       <c r="X172" s="22" t="n">
-        <v>3.443</v>
+        <v>-92.08199999999999</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>법인세 환급</t>
         </is>
       </c>
       <c r="E173" s="22" t="n">
-        <v>-54.513</v>
+        <v>494.965</v>
       </c>
       <c r="I173" s="22" t="n">
-        <v>-40.359</v>
+        <v>17.56</v>
       </c>
       <c r="M173" s="22" t="n">
-        <v>-79.14700000000001</v>
-      </c>
-      <c r="O173" s="22" t="n">
-        <v>-67.18600000000001</v>
-      </c>
-      <c r="P173" s="22" t="n">
-        <v>-98.616</v>
-      </c>
-      <c r="Q173" s="22" t="n">
-        <v>-44.784</v>
-      </c>
-      <c r="R173" s="22" t="n">
-        <v>-71.246</v>
-      </c>
-      <c r="S173" s="22" t="n">
-        <v>-40.97</v>
-      </c>
-      <c r="T173" s="22" t="n">
-        <v>-48.867</v>
-      </c>
-      <c r="U173" s="22" t="n">
-        <v>-37.068</v>
+        <v>11.957</v>
       </c>
       <c r="V173" s="22" t="n">
-        <v>-54.513</v>
+        <v>494.965</v>
       </c>
       <c r="W173" s="22" t="n">
-        <v>-40.359</v>
+        <v>17.56</v>
       </c>
       <c r="X173" s="22" t="n">
-        <v>-79.14700000000001</v>
+        <v>11.957</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="20" t="inlineStr">
-        <is>
-          <t>투자유가증권 취득</t>
-        </is>
-      </c>
-      <c r="E174" s="22" t="n">
-        <v>-100</v>
-      </c>
-      <c r="I174" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q174" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R174" s="22" t="n">
-        <v>-5.701</v>
-      </c>
-      <c r="S174" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T174" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U174" s="22" t="n">
-        <v>-100</v>
-      </c>
-      <c r="V174" s="22" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W174" s="22" t="n">
-        <v>0</v>
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E174" s="12" t="n">
+        <v>2705.164</v>
+      </c>
+      <c r="I174" s="12" t="n">
+        <v>1450.576</v>
+      </c>
+      <c r="M174" s="12" t="n">
+        <v>878.904</v>
+      </c>
+      <c r="O174" s="12" t="n">
+        <v>5858.584</v>
+      </c>
+      <c r="P174" s="12" t="n">
+        <v>8167.901</v>
+      </c>
+      <c r="Q174" s="12" t="n">
+        <v>7480.95</v>
+      </c>
+      <c r="R174" s="12" t="n">
+        <v>3481.075</v>
+      </c>
+      <c r="S174" s="12" t="n">
+        <v>4575.701</v>
+      </c>
+      <c r="T174" s="12" t="n">
+        <v>4031.117</v>
+      </c>
+      <c r="U174" s="12" t="n">
+        <v>3588.261</v>
+      </c>
+      <c r="V174" s="12" t="n">
+        <v>2705.164</v>
+      </c>
+      <c r="W174" s="12" t="n">
+        <v>1450.576</v>
+      </c>
+      <c r="X174" s="12" t="n">
+        <v>878.904</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각</t>
+          <t>정기예금 예입</t>
         </is>
       </c>
       <c r="E175" s="22" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="I175" s="22" t="n">
-        <v>17.76</v>
+        <v>-4000</v>
       </c>
       <c r="M175" s="22" t="n">
-        <v>11.05</v>
+        <v>0</v>
       </c>
       <c r="O175" s="22" t="n">
-        <v>202.653</v>
+        <v>-1128.7</v>
       </c>
       <c r="P175" s="22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q175" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="R175" s="22" t="n">
-        <v>5.847</v>
-      </c>
-      <c r="S175" s="22" t="n">
-        <v>62.387</v>
-      </c>
-      <c r="T175" s="22" t="n">
+      <c r="V175" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="U175" s="22" t="n">
+      <c r="W175" s="22" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="X175" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="V175" s="22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="W175" s="22" t="n">
-        <v>17.76</v>
-      </c>
-      <c r="X175" s="22" t="n">
-        <v>11.05</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 취득</t>
-        </is>
-      </c>
-      <c r="O176" s="22" t="n">
-        <v>-614.5170000000001</v>
+          <t>정기예금 인출</t>
+        </is>
+      </c>
+      <c r="I176" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="22" t="n">
+        <v>4000</v>
       </c>
       <c r="P176" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="Q176" s="22" t="n">
+        <v>1128.7</v>
+      </c>
+      <c r="R176" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W176" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X176" s="22" t="n">
+        <v>4000</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="20" t="inlineStr">
         <is>
-          <t>보험적립금 환급</t>
-        </is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="E177" s="22" t="n">
+        <v>-2943.406</v>
+      </c>
+      <c r="I177" s="22" t="n">
+        <v>-3851.746</v>
+      </c>
+      <c r="M177" s="22" t="n">
+        <v>-11359.851</v>
       </c>
       <c r="O177" s="22" t="n">
-        <v>100.607</v>
+        <v>-2747.07</v>
       </c>
       <c r="P177" s="22" t="n">
-        <v>0</v>
+        <v>-4744.546</v>
+      </c>
+      <c r="Q177" s="22" t="n">
+        <v>-4037.514</v>
+      </c>
+      <c r="R177" s="22" t="n">
+        <v>-3929.121</v>
+      </c>
+      <c r="S177" s="22" t="n">
+        <v>-2488.374</v>
+      </c>
+      <c r="T177" s="22" t="n">
+        <v>-2678.123</v>
+      </c>
+      <c r="U177" s="22" t="n">
+        <v>-3725.477</v>
+      </c>
+      <c r="V177" s="22" t="n">
+        <v>-2943.406</v>
+      </c>
+      <c r="W177" s="22" t="n">
+        <v>-3851.746</v>
+      </c>
+      <c r="X177" s="22" t="n">
+        <v>-11359.851</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="20" t="inlineStr">
         <is>
-          <t>보증금 회수</t>
-        </is>
+          <t>유형자산 제각 지출</t>
+        </is>
+      </c>
+      <c r="E178" s="22" t="n">
+        <v>-137.999</v>
+      </c>
+      <c r="I178" s="22" t="n">
+        <v>-33.658</v>
+      </c>
+      <c r="M178" s="22" t="n">
+        <v>-135.607</v>
       </c>
       <c r="O178" s="22" t="n">
-        <v>0.063</v>
+        <v>-1.616</v>
       </c>
       <c r="P178" s="22" t="n">
-        <v>0.439</v>
+        <v>-3.558</v>
+      </c>
+      <c r="Q178" s="22" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="R178" s="22" t="n">
+        <v>-8.971</v>
+      </c>
+      <c r="S178" s="22" t="n">
+        <v>-5.159</v>
+      </c>
+      <c r="T178" s="22" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="U178" s="22" t="n">
+        <v>-47.657</v>
+      </c>
+      <c r="V178" s="22" t="n">
+        <v>-137.999</v>
+      </c>
+      <c r="W178" s="22" t="n">
+        <v>-33.658</v>
+      </c>
+      <c r="X178" s="22" t="n">
+        <v>-135.607</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="20" t="inlineStr">
         <is>
-          <t>기타 지출</t>
-        </is>
+          <t>유형자산 매각</t>
+        </is>
+      </c>
+      <c r="E179" s="22" t="n">
+        <v>167.063</v>
+      </c>
+      <c r="I179" s="22" t="n">
+        <v>2.381</v>
+      </c>
+      <c r="M179" s="22" t="n">
+        <v>3.443</v>
       </c>
       <c r="O179" s="22" t="n">
-        <v>-37.857</v>
+        <v>0.155</v>
       </c>
       <c r="P179" s="22" t="n">
-        <v>-32.923</v>
+        <v>2.61</v>
+      </c>
+      <c r="Q179" s="22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="R179" s="22" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="S179" s="22" t="n">
+        <v>12.529</v>
+      </c>
+      <c r="T179" s="22" t="n">
+        <v>14.148</v>
+      </c>
+      <c r="U179" s="22" t="n">
+        <v>28.618</v>
+      </c>
+      <c r="V179" s="22" t="n">
+        <v>167.063</v>
+      </c>
+      <c r="W179" s="22" t="n">
+        <v>2.381</v>
+      </c>
+      <c r="X179" s="22" t="n">
+        <v>3.443</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>무형자산 취득</t>
         </is>
       </c>
       <c r="E180" s="22" t="n">
-        <v>102.36</v>
+        <v>-54.513</v>
       </c>
       <c r="I180" s="22" t="n">
-        <v>53.257</v>
+        <v>-40.359</v>
       </c>
       <c r="M180" s="22" t="n">
-        <v>-87.327</v>
+        <v>-79.14700000000001</v>
+      </c>
+      <c r="O180" s="22" t="n">
+        <v>-67.18600000000001</v>
       </c>
       <c r="P180" s="22" t="n">
-        <v>-32.484</v>
+        <v>-98.616</v>
       </c>
       <c r="Q180" s="22" t="n">
-        <v>-26.865</v>
+        <v>-44.784</v>
       </c>
       <c r="R180" s="22" t="n">
-        <v>-39.28</v>
+        <v>-71.246</v>
       </c>
       <c r="S180" s="22" t="n">
-        <v>9.257</v>
+        <v>-40.97</v>
       </c>
       <c r="T180" s="22" t="n">
-        <v>43.44</v>
+        <v>-48.867</v>
       </c>
       <c r="U180" s="22" t="n">
-        <v>31.303</v>
+        <v>-37.068</v>
       </c>
       <c r="V180" s="22" t="n">
-        <v>102.36</v>
+        <v>-54.513</v>
       </c>
       <c r="W180" s="22" t="n">
-        <v>53.257</v>
+        <v>-40.359</v>
       </c>
       <c r="X180" s="22" t="n">
-        <v>-87.327</v>
+        <v>-79.14700000000001</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E181" s="12" t="n">
-        <v>-2964.185</v>
-      </c>
-      <c r="I181" s="12" t="n">
-        <v>-7852.366</v>
-      </c>
-      <c r="M181" s="12" t="n">
-        <v>-7647.44</v>
-      </c>
-      <c r="O181" s="12" t="n">
-        <v>-4293.467</v>
-      </c>
-      <c r="P181" s="12" t="n">
-        <v>-4875.493</v>
-      </c>
-      <c r="Q181" s="12" t="n">
-        <v>-2981.204</v>
-      </c>
-      <c r="R181" s="12" t="n">
-        <v>-4048.432</v>
-      </c>
-      <c r="S181" s="12" t="n">
-        <v>-2450.328</v>
-      </c>
-      <c r="T181" s="12" t="n">
-        <v>-2683.802</v>
-      </c>
-      <c r="U181" s="12" t="n">
-        <v>-3850.281</v>
-      </c>
-      <c r="V181" s="12" t="n">
-        <v>-2964.185</v>
-      </c>
-      <c r="W181" s="12" t="n">
-        <v>-7852.366</v>
-      </c>
-      <c r="X181" s="12" t="n">
-        <v>-7647.44</v>
+      <c r="A181" s="20" t="inlineStr">
+        <is>
+          <t>투자유가증권 취득</t>
+        </is>
+      </c>
+      <c r="E181" s="22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I181" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" s="22" t="n">
+        <v>-5.701</v>
+      </c>
+      <c r="S181" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" s="22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="V181" s="22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W181" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="20" t="inlineStr">
         <is>
-          <t>단기차입</t>
+          <t>투자유가증권 매각</t>
         </is>
       </c>
       <c r="E182" s="22" t="n">
-        <v>1140</v>
+        <v>2.31</v>
       </c>
       <c r="I182" s="22" t="n">
-        <v>2130</v>
+        <v>17.76</v>
       </c>
       <c r="M182" s="22" t="n">
-        <v>1200</v>
+        <v>11.05</v>
       </c>
       <c r="O182" s="22" t="n">
-        <v>1140</v>
+        <v>202.653</v>
       </c>
       <c r="P182" s="22" t="n">
-        <v>1140</v>
+        <v>1.1</v>
       </c>
       <c r="Q182" s="22" t="n">
-        <v>1140</v>
+        <v>0</v>
       </c>
       <c r="R182" s="22" t="n">
-        <v>1140</v>
+        <v>5.847</v>
       </c>
       <c r="S182" s="22" t="n">
-        <v>1140</v>
+        <v>62.387</v>
       </c>
       <c r="T182" s="22" t="n">
-        <v>1140</v>
+        <v>0</v>
       </c>
       <c r="U182" s="22" t="n">
-        <v>1140</v>
+        <v>0</v>
       </c>
       <c r="V182" s="22" t="n">
-        <v>1140</v>
+        <v>2.31</v>
       </c>
       <c r="W182" s="22" t="n">
-        <v>2130</v>
+        <v>17.76</v>
       </c>
       <c r="X182" s="22" t="n">
-        <v>1200</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="20" t="inlineStr">
         <is>
-          <t>단기차입금 상환</t>
-        </is>
-      </c>
-      <c r="E183" s="22" t="n">
-        <v>-1140</v>
-      </c>
-      <c r="I183" s="22" t="n">
-        <v>-1140</v>
-      </c>
-      <c r="M183" s="22" t="n">
-        <v>-1490</v>
+          <t>연결범위 변경 자회사 주식 취득</t>
+        </is>
       </c>
       <c r="O183" s="22" t="n">
-        <v>-1140</v>
+        <v>-614.5170000000001</v>
       </c>
       <c r="P183" s="22" t="n">
-        <v>-1140</v>
-      </c>
-      <c r="Q183" s="22" t="n">
-        <v>-1140</v>
-      </c>
-      <c r="R183" s="22" t="n">
-        <v>-1140</v>
-      </c>
-      <c r="S183" s="22" t="n">
-        <v>-1140</v>
-      </c>
-      <c r="T183" s="22" t="n">
-        <v>-1140</v>
-      </c>
-      <c r="U183" s="22" t="n">
-        <v>-1140</v>
-      </c>
-      <c r="V183" s="22" t="n">
-        <v>-1140</v>
-      </c>
-      <c r="W183" s="22" t="n">
-        <v>-1140</v>
-      </c>
-      <c r="X183" s="22" t="n">
-        <v>-1490</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="20" t="inlineStr">
         <is>
-          <t>장기차입</t>
-        </is>
-      </c>
-      <c r="E184" s="22" t="n">
-        <v>630</v>
-      </c>
-      <c r="I184" s="22" t="n">
+          <t>보험적립금 환급</t>
+        </is>
+      </c>
+      <c r="O184" s="22" t="n">
+        <v>100.607</v>
+      </c>
+      <c r="P184" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="M184" s="22" t="n">
-        <v>8475</v>
-      </c>
-      <c r="O184" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P184" s="22" t="n">
-        <v>400</v>
-      </c>
-      <c r="Q184" s="22" t="n">
-        <v>630</v>
-      </c>
-      <c r="R184" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S184" s="22" t="n">
-        <v>500</v>
-      </c>
-      <c r="T184" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U184" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V184" s="22" t="n">
-        <v>630</v>
-      </c>
-      <c r="W184" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X184" s="22" t="n">
-        <v>8475</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="20" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
-        </is>
-      </c>
-      <c r="E185" s="22" t="n">
-        <v>-224.496</v>
-      </c>
-      <c r="I185" s="22" t="n">
-        <v>-233.496</v>
-      </c>
-      <c r="M185" s="22" t="n">
-        <v>-167.685</v>
+          <t>보증금 회수</t>
+        </is>
       </c>
       <c r="O185" s="22" t="n">
-        <v>-459.188</v>
+        <v>0.063</v>
       </c>
       <c r="P185" s="22" t="n">
-        <v>-559.188</v>
-      </c>
-      <c r="Q185" s="22" t="n">
-        <v>-387.748</v>
-      </c>
-      <c r="R185" s="22" t="n">
-        <v>-264.612</v>
-      </c>
-      <c r="S185" s="22" t="n">
-        <v>-288.76</v>
-      </c>
-      <c r="T185" s="22" t="n">
-        <v>-305.988</v>
-      </c>
-      <c r="U185" s="22" t="n">
-        <v>-306.028</v>
-      </c>
-      <c r="V185" s="22" t="n">
-        <v>-224.496</v>
-      </c>
-      <c r="W185" s="22" t="n">
-        <v>-233.496</v>
-      </c>
-      <c r="X185" s="22" t="n">
-        <v>-167.685</v>
+        <v>0.439</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="20" t="inlineStr">
         <is>
-          <t>리스부채 상환</t>
-        </is>
-      </c>
-      <c r="E186" s="22" t="n">
-        <v>-65.09399999999999</v>
-      </c>
-      <c r="I186" s="22" t="n">
-        <v>-58.792</v>
-      </c>
-      <c r="M186" s="22" t="n">
-        <v>-43.435</v>
+          <t>기타 지출</t>
+        </is>
       </c>
       <c r="O186" s="22" t="n">
-        <v>-89.59</v>
+        <v>-37.857</v>
       </c>
       <c r="P186" s="22" t="n">
-        <v>-229.241</v>
-      </c>
-      <c r="Q186" s="22" t="n">
-        <v>-352.419</v>
-      </c>
-      <c r="R186" s="22" t="n">
-        <v>-343.804</v>
-      </c>
-      <c r="S186" s="22" t="n">
-        <v>-82.34999999999999</v>
-      </c>
-      <c r="T186" s="22" t="n">
-        <v>-74.36199999999999</v>
-      </c>
-      <c r="U186" s="22" t="n">
-        <v>-67.218</v>
-      </c>
-      <c r="V186" s="22" t="n">
-        <v>-65.09399999999999</v>
-      </c>
-      <c r="W186" s="22" t="n">
-        <v>-58.792</v>
-      </c>
-      <c r="X186" s="22" t="n">
-        <v>-43.435</v>
+        <v>-32.923</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="20" t="inlineStr">
         <is>
-          <t>Repayments Of Installment Payables Fin CF</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E187" s="22" t="n">
-        <v>0</v>
+        <v>102.36</v>
+      </c>
+      <c r="I187" s="22" t="n">
+        <v>53.257</v>
+      </c>
+      <c r="M187" s="22" t="n">
+        <v>-87.327</v>
+      </c>
+      <c r="P187" s="22" t="n">
+        <v>-32.484</v>
+      </c>
+      <c r="Q187" s="22" t="n">
+        <v>-26.865</v>
+      </c>
+      <c r="R187" s="22" t="n">
+        <v>-39.28</v>
       </c>
       <c r="S187" s="22" t="n">
-        <v>-548.954</v>
+        <v>9.257</v>
       </c>
       <c r="T187" s="22" t="n">
-        <v>-539.754</v>
+        <v>43.44</v>
       </c>
       <c r="U187" s="22" t="n">
-        <v>-373.618</v>
+        <v>31.303</v>
       </c>
       <c r="V187" s="22" t="n">
-        <v>0</v>
+        <v>102.36</v>
+      </c>
+      <c r="W187" s="22" t="n">
+        <v>53.257</v>
+      </c>
+      <c r="X187" s="22" t="n">
+        <v>-87.327</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="20" t="inlineStr">
-        <is>
-          <t>배당금 지급</t>
-        </is>
-      </c>
-      <c r="E188" s="22" t="n">
-        <v>-647.947</v>
-      </c>
-      <c r="I188" s="22" t="n">
-        <v>-604.746</v>
-      </c>
-      <c r="M188" s="22" t="n">
-        <v>-604.7430000000001</v>
-      </c>
-      <c r="O188" s="22" t="n">
-        <v>-635.965</v>
-      </c>
-      <c r="P188" s="22" t="n">
-        <v>-647.962</v>
-      </c>
-      <c r="Q188" s="22" t="n">
-        <v>-671.96</v>
-      </c>
-      <c r="R188" s="22" t="n">
-        <v>-791.953</v>
-      </c>
-      <c r="S188" s="22" t="n">
-        <v>-671.956</v>
-      </c>
-      <c r="T188" s="22" t="n">
-        <v>-671.949</v>
-      </c>
-      <c r="U188" s="22" t="n">
-        <v>-671.949</v>
-      </c>
-      <c r="V188" s="22" t="n">
-        <v>-647.947</v>
-      </c>
-      <c r="W188" s="22" t="n">
-        <v>-604.746</v>
-      </c>
-      <c r="X188" s="22" t="n">
-        <v>-604.7430000000001</v>
+      <c r="A188" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E188" s="12" t="n">
+        <v>-2964.185</v>
+      </c>
+      <c r="I188" s="12" t="n">
+        <v>-7852.366</v>
+      </c>
+      <c r="M188" s="12" t="n">
+        <v>-7647.44</v>
+      </c>
+      <c r="O188" s="12" t="n">
+        <v>-4293.467</v>
+      </c>
+      <c r="P188" s="12" t="n">
+        <v>-4875.493</v>
+      </c>
+      <c r="Q188" s="12" t="n">
+        <v>-2981.204</v>
+      </c>
+      <c r="R188" s="12" t="n">
+        <v>-4048.432</v>
+      </c>
+      <c r="S188" s="12" t="n">
+        <v>-2450.328</v>
+      </c>
+      <c r="T188" s="12" t="n">
+        <v>-2683.802</v>
+      </c>
+      <c r="U188" s="12" t="n">
+        <v>-3850.281</v>
+      </c>
+      <c r="V188" s="12" t="n">
+        <v>-2964.185</v>
+      </c>
+      <c r="W188" s="12" t="n">
+        <v>-7852.366</v>
+      </c>
+      <c r="X188" s="12" t="n">
+        <v>-7647.44</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
+          <t>단기차입</t>
         </is>
       </c>
       <c r="E189" s="22" t="n">
-        <v>-1959.2</v>
+        <v>1140</v>
       </c>
       <c r="I189" s="22" t="n">
-        <v>-0.141</v>
+        <v>2130</v>
       </c>
       <c r="M189" s="22" t="n">
-        <v>-0.059</v>
+        <v>1200</v>
       </c>
       <c r="O189" s="22" t="n">
-        <v>-0.205</v>
+        <v>1140</v>
       </c>
       <c r="P189" s="22" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="Q189" s="22" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="R189" s="22" t="n">
-        <v>-0.132</v>
+        <v>1140</v>
       </c>
       <c r="S189" s="22" t="n">
-        <v>-0.329</v>
+        <v>1140</v>
       </c>
       <c r="T189" s="22" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="U189" s="22" t="n">
-        <v>-0.147</v>
+        <v>1140</v>
       </c>
       <c r="V189" s="22" t="n">
-        <v>-1959.2</v>
+        <v>1140</v>
       </c>
       <c r="W189" s="22" t="n">
-        <v>-0.141</v>
+        <v>2130</v>
       </c>
       <c r="X189" s="22" t="n">
-        <v>-0.059</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E190" s="12" t="n">
-        <v>-2266.737</v>
-      </c>
-      <c r="I190" s="12" t="n">
-        <v>92.82299999999999</v>
-      </c>
-      <c r="M190" s="12" t="n">
-        <v>7369.076</v>
-      </c>
-      <c r="O190" s="12" t="n">
-        <v>-1184.949</v>
-      </c>
-      <c r="P190" s="12" t="n">
-        <v>-1036.391</v>
-      </c>
-      <c r="Q190" s="12" t="n">
-        <v>-782.128</v>
-      </c>
-      <c r="R190" s="12" t="n">
-        <v>-1400.502</v>
-      </c>
-      <c r="S190" s="12" t="n">
-        <v>-1092.351</v>
-      </c>
-      <c r="T190" s="12" t="n">
-        <v>-1592.054</v>
-      </c>
-      <c r="U190" s="12" t="n">
-        <v>-1418.961</v>
-      </c>
-      <c r="V190" s="12" t="n">
-        <v>-2266.737</v>
-      </c>
-      <c r="W190" s="12" t="n">
-        <v>92.82299999999999</v>
-      </c>
-      <c r="X190" s="12" t="n">
-        <v>7369.076</v>
+      <c r="A190" s="20" t="inlineStr">
+        <is>
+          <t>단기차입금 상환</t>
+        </is>
+      </c>
+      <c r="E190" s="22" t="n">
+        <v>-1140</v>
+      </c>
+      <c r="I190" s="22" t="n">
+        <v>-1140</v>
+      </c>
+      <c r="M190" s="22" t="n">
+        <v>-1490</v>
+      </c>
+      <c r="O190" s="22" t="n">
+        <v>-1140</v>
+      </c>
+      <c r="P190" s="22" t="n">
+        <v>-1140</v>
+      </c>
+      <c r="Q190" s="22" t="n">
+        <v>-1140</v>
+      </c>
+      <c r="R190" s="22" t="n">
+        <v>-1140</v>
+      </c>
+      <c r="S190" s="22" t="n">
+        <v>-1140</v>
+      </c>
+      <c r="T190" s="22" t="n">
+        <v>-1140</v>
+      </c>
+      <c r="U190" s="22" t="n">
+        <v>-1140</v>
+      </c>
+      <c r="V190" s="22" t="n">
+        <v>-1140</v>
+      </c>
+      <c r="W190" s="22" t="n">
+        <v>-1140</v>
+      </c>
+      <c r="X190" s="22" t="n">
+        <v>-1490</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
+          <t>장기차입</t>
         </is>
       </c>
       <c r="E191" s="22" t="n">
-        <v>20.494</v>
+        <v>630</v>
       </c>
       <c r="I191" s="22" t="n">
-        <v>-46.481</v>
+        <v>0</v>
       </c>
       <c r="M191" s="22" t="n">
-        <v>44.939</v>
+        <v>8475</v>
       </c>
       <c r="O191" s="22" t="n">
-        <v>-254.298</v>
+        <v>0</v>
       </c>
       <c r="P191" s="22" t="n">
-        <v>-135.973</v>
+        <v>400</v>
       </c>
       <c r="Q191" s="22" t="n">
-        <v>31.495</v>
+        <v>630</v>
       </c>
       <c r="R191" s="22" t="n">
-        <v>37.186</v>
+        <v>0</v>
       </c>
       <c r="S191" s="22" t="n">
-        <v>18.785</v>
+        <v>500</v>
       </c>
       <c r="T191" s="22" t="n">
-        <v>315.079</v>
+        <v>0</v>
       </c>
       <c r="U191" s="22" t="n">
-        <v>128.483</v>
+        <v>0</v>
       </c>
       <c r="V191" s="22" t="n">
-        <v>20.494</v>
+        <v>630</v>
       </c>
       <c r="W191" s="22" t="n">
-        <v>-46.481</v>
+        <v>0</v>
       </c>
       <c r="X191" s="22" t="n">
-        <v>44.939</v>
+        <v>8475</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="20" t="inlineStr">
         <is>
+          <t>장기차입금 상환</t>
+        </is>
+      </c>
+      <c r="E192" s="22" t="n">
+        <v>-224.496</v>
+      </c>
+      <c r="I192" s="22" t="n">
+        <v>-233.496</v>
+      </c>
+      <c r="M192" s="22" t="n">
+        <v>-167.685</v>
+      </c>
+      <c r="O192" s="22" t="n">
+        <v>-459.188</v>
+      </c>
+      <c r="P192" s="22" t="n">
+        <v>-559.188</v>
+      </c>
+      <c r="Q192" s="22" t="n">
+        <v>-387.748</v>
+      </c>
+      <c r="R192" s="22" t="n">
+        <v>-264.612</v>
+      </c>
+      <c r="S192" s="22" t="n">
+        <v>-288.76</v>
+      </c>
+      <c r="T192" s="22" t="n">
+        <v>-305.988</v>
+      </c>
+      <c r="U192" s="22" t="n">
+        <v>-306.028</v>
+      </c>
+      <c r="V192" s="22" t="n">
+        <v>-224.496</v>
+      </c>
+      <c r="W192" s="22" t="n">
+        <v>-233.496</v>
+      </c>
+      <c r="X192" s="22" t="n">
+        <v>-167.685</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="20" t="inlineStr">
+        <is>
+          <t>리스부채 상환</t>
+        </is>
+      </c>
+      <c r="E193" s="22" t="n">
+        <v>-65.09399999999999</v>
+      </c>
+      <c r="I193" s="22" t="n">
+        <v>-58.792</v>
+      </c>
+      <c r="M193" s="22" t="n">
+        <v>-43.435</v>
+      </c>
+      <c r="O193" s="22" t="n">
+        <v>-89.59</v>
+      </c>
+      <c r="P193" s="22" t="n">
+        <v>-229.241</v>
+      </c>
+      <c r="Q193" s="22" t="n">
+        <v>-352.419</v>
+      </c>
+      <c r="R193" s="22" t="n">
+        <v>-343.804</v>
+      </c>
+      <c r="S193" s="22" t="n">
+        <v>-82.34999999999999</v>
+      </c>
+      <c r="T193" s="22" t="n">
+        <v>-74.36199999999999</v>
+      </c>
+      <c r="U193" s="22" t="n">
+        <v>-67.218</v>
+      </c>
+      <c r="V193" s="22" t="n">
+        <v>-65.09399999999999</v>
+      </c>
+      <c r="W193" s="22" t="n">
+        <v>-58.792</v>
+      </c>
+      <c r="X193" s="22" t="n">
+        <v>-43.435</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="20" t="inlineStr">
+        <is>
+          <t>Repayments Of Installment Payables Fin CF</t>
+        </is>
+      </c>
+      <c r="E194" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" s="22" t="n">
+        <v>-548.954</v>
+      </c>
+      <c r="T194" s="22" t="n">
+        <v>-539.754</v>
+      </c>
+      <c r="U194" s="22" t="n">
+        <v>-373.618</v>
+      </c>
+      <c r="V194" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="E195" s="22" t="n">
+        <v>-647.947</v>
+      </c>
+      <c r="I195" s="22" t="n">
+        <v>-604.746</v>
+      </c>
+      <c r="M195" s="22" t="n">
+        <v>-604.7430000000001</v>
+      </c>
+      <c r="O195" s="22" t="n">
+        <v>-635.965</v>
+      </c>
+      <c r="P195" s="22" t="n">
+        <v>-647.962</v>
+      </c>
+      <c r="Q195" s="22" t="n">
+        <v>-671.96</v>
+      </c>
+      <c r="R195" s="22" t="n">
+        <v>-791.953</v>
+      </c>
+      <c r="S195" s="22" t="n">
+        <v>-671.956</v>
+      </c>
+      <c r="T195" s="22" t="n">
+        <v>-671.949</v>
+      </c>
+      <c r="U195" s="22" t="n">
+        <v>-671.949</v>
+      </c>
+      <c r="V195" s="22" t="n">
+        <v>-647.947</v>
+      </c>
+      <c r="W195" s="22" t="n">
+        <v>-604.746</v>
+      </c>
+      <c r="X195" s="22" t="n">
+        <v>-604.7430000000001</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="E196" s="22" t="n">
+        <v>-1959.2</v>
+      </c>
+      <c r="I196" s="22" t="n">
+        <v>-0.141</v>
+      </c>
+      <c r="M196" s="22" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="O196" s="22" t="n">
+        <v>-0.205</v>
+      </c>
+      <c r="P196" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q196" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R196" s="22" t="n">
+        <v>-0.132</v>
+      </c>
+      <c r="S196" s="22" t="n">
+        <v>-0.329</v>
+      </c>
+      <c r="T196" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" s="22" t="n">
+        <v>-0.147</v>
+      </c>
+      <c r="V196" s="22" t="n">
+        <v>-1959.2</v>
+      </c>
+      <c r="W196" s="22" t="n">
+        <v>-0.141</v>
+      </c>
+      <c r="X196" s="22" t="n">
+        <v>-0.059</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E197" s="12" t="n">
+        <v>-2266.737</v>
+      </c>
+      <c r="I197" s="12" t="n">
+        <v>92.82299999999999</v>
+      </c>
+      <c r="M197" s="12" t="n">
+        <v>7369.076</v>
+      </c>
+      <c r="O197" s="12" t="n">
+        <v>-1184.949</v>
+      </c>
+      <c r="P197" s="12" t="n">
+        <v>-1036.391</v>
+      </c>
+      <c r="Q197" s="12" t="n">
+        <v>-782.128</v>
+      </c>
+      <c r="R197" s="12" t="n">
+        <v>-1400.502</v>
+      </c>
+      <c r="S197" s="12" t="n">
+        <v>-1092.351</v>
+      </c>
+      <c r="T197" s="12" t="n">
+        <v>-1592.054</v>
+      </c>
+      <c r="U197" s="12" t="n">
+        <v>-1418.961</v>
+      </c>
+      <c r="V197" s="12" t="n">
+        <v>-2266.737</v>
+      </c>
+      <c r="W197" s="12" t="n">
+        <v>92.82299999999999</v>
+      </c>
+      <c r="X197" s="12" t="n">
+        <v>7369.076</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="E198" s="22" t="n">
+        <v>20.494</v>
+      </c>
+      <c r="I198" s="22" t="n">
+        <v>-46.481</v>
+      </c>
+      <c r="M198" s="22" t="n">
+        <v>44.939</v>
+      </c>
+      <c r="O198" s="22" t="n">
+        <v>-254.298</v>
+      </c>
+      <c r="P198" s="22" t="n">
+        <v>-135.973</v>
+      </c>
+      <c r="Q198" s="22" t="n">
+        <v>31.495</v>
+      </c>
+      <c r="R198" s="22" t="n">
+        <v>37.186</v>
+      </c>
+      <c r="S198" s="22" t="n">
+        <v>18.785</v>
+      </c>
+      <c r="T198" s="22" t="n">
+        <v>315.079</v>
+      </c>
+      <c r="U198" s="22" t="n">
+        <v>128.483</v>
+      </c>
+      <c r="V198" s="22" t="n">
+        <v>20.494</v>
+      </c>
+      <c r="W198" s="22" t="n">
+        <v>-46.481</v>
+      </c>
+      <c r="X198" s="22" t="n">
+        <v>44.939</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="E192" s="22" t="n">
+      <c r="E199" s="22" t="n">
         <v>-2505.264</v>
       </c>
-      <c r="I192" s="22" t="n">
+      <c r="I199" s="22" t="n">
         <v>-6355.447</v>
       </c>
-      <c r="M192" s="22" t="n">
+      <c r="M199" s="22" t="n">
         <v>645.479</v>
       </c>
-      <c r="O192" s="22" t="n">
+      <c r="O199" s="22" t="n">
         <v>125.869</v>
       </c>
-      <c r="P192" s="22" t="n">
+      <c r="P199" s="22" t="n">
         <v>2120.042</v>
       </c>
-      <c r="Q192" s="22" t="n">
+      <c r="Q199" s="22" t="n">
         <v>3749.113</v>
       </c>
-      <c r="R192" s="22" t="n">
+      <c r="R199" s="22" t="n">
         <v>-1930.672</v>
       </c>
-      <c r="S192" s="22" t="n">
+      <c r="S199" s="22" t="n">
         <v>1051.806</v>
       </c>
-      <c r="T192" s="22" t="n">
+      <c r="T199" s="22" t="n">
         <v>70.34</v>
       </c>
-      <c r="U192" s="22" t="n">
+      <c r="U199" s="22" t="n">
         <v>-1552.498</v>
       </c>
-      <c r="V192" s="22" t="n">
+      <c r="V199" s="22" t="n">
         <v>-2505.264</v>
       </c>
-      <c r="W192" s="22" t="n">
+      <c r="W199" s="22" t="n">
         <v>-6355.447</v>
       </c>
-      <c r="X192" s="22" t="n">
+      <c r="X199" s="22" t="n">
         <v>645.479</v>
       </c>
     </row>
@@ -10893,7 +11364,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -12355,7 +12826,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -12407,7 +12878,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -12459,7 +12930,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -12511,7 +12982,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -12563,7 +13034,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -12615,7 +13086,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -12667,7 +13138,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -12677,43 +13148,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -12737,7 +13208,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -12789,7 +13260,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -12841,7 +13312,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -12893,7 +13364,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -12945,7 +13416,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -12997,7 +13468,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -13067,7 +13538,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -13119,7 +13590,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -13129,49 +13600,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -13181,49 +13652,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -13233,49 +13704,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -13285,43 +13756,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -13345,7 +13816,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -13397,7 +13868,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -13449,7 +13920,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -13501,7 +13972,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -16043,24 +16514,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
